--- a/Iso_Fest_Tracker.xlsx
+++ b/Iso_Fest_Tracker.xlsx
@@ -21,7 +21,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="169" uniqueCount="103">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="221" uniqueCount="130">
   <si>
     <t xml:space="preserve">Iso Fest Milestones</t>
   </si>
@@ -281,40 +281,121 @@
     <t xml:space="preserve">Notes</t>
   </si>
   <si>
+    <t xml:space="preserve">Daily</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Log in</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Once a day</t>
+  </si>
+  <si>
     <t xml:space="preserve">Spend</t>
   </si>
   <si>
-    <t xml:space="preserve">Spend 1 Gold</t>
+    <t xml:space="preserve">Spend Gold</t>
   </si>
   <si>
     <t xml:space="preserve">Planned is current gold plus the Thu and Sun Gold Rushes</t>
   </si>
   <si>
-    <t xml:space="preserve">Spend 1 Power Core</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Also counted cores spent before Iron Vengeance began</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Spend 1 Orange training material</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Orange comes from Training Day and basic training orbs</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Spend 1 Tier 2 Ion</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Needs tier 2 iso, which needs level 75</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Spend 1 Tier 3 Ion</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Points each not confirmed yet, fill from the task list</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Spare row for tasks not listed yet</t>
+    <t xml:space="preserve">Spend Power Cores</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Includes cores spent before Iron Vengeance began</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Spend L4 Training Modules (orange)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Ions</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Spend 1 Tier 2 Level 5 Ion</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Spend 1 Tier 2 Level 4 Ion</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Spend 1 Tier 2 Level 1 Ion</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Spend 1 Tier 3 Level 5 Ion</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Unlimited. Game doesn't show earned</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Spend 1 Tier 3 Level 4 Ion</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Spend 1 Tier 3 Level 1 Ion</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Spend 1 Tier 4 Level 1 Ion</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Upgrade</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Insidious Six to T3 L4</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Planned is number of upgrades</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Insidious Six to T3 L5</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Symbiote Six to T3 L4</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Symbiote Six to T3 L5</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Amazing Avenger to T3 L4</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Amazing Avenger to T3 L5</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Cosmic character to T3 L5</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Mephisto planned after milestone 24</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Global character to T3 L5</t>
+  </si>
+  <si>
+    <t xml:space="preserve">City character to T3 L5</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Cosmic character to T4 L3</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Global character to T4 L3</t>
+  </si>
+  <si>
+    <t xml:space="preserve">City character to T4 L3</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Offers</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Earn Iso Fest milestone points in select offers</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Unlimited</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Spare row</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Earned from tasks with a limit</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Unlimited tasks, ions and offers</t>
   </si>
   <si>
     <t xml:space="preserve">Points from planned spending</t>
@@ -941,8 +1022,8 @@
         <v>15</v>
       </c>
       <c r="G9" s="7" t="n">
-        <f aca="false">Scoring!B18</f>
-        <v>492196315</v>
+        <f aca="false">Scoring!B36</f>
+        <v>497196315</v>
       </c>
     </row>
     <row r="10" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -957,7 +1038,7 @@
         <v>17</v>
       </c>
       <c r="G10" s="7" t="n">
-        <f aca="false">Scoring!B19</f>
+        <f aca="false">Scoring!B37</f>
         <v>22</v>
       </c>
     </row>
@@ -967,7 +1048,7 @@
       </c>
       <c r="B11" s="7" t="n">
         <f aca="true">IFERROR(B10/MAX(B5-NOW(),0.01),0)</f>
-        <v>28119941.5833071</v>
+        <v>28138403.026481</v>
       </c>
     </row>
     <row r="12" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -2214,7 +2295,7 @@
   <sheetPr filterMode="false">
     <pageSetUpPr fitToPage="false"/>
   </sheetPr>
-  <dimension ref="A1:I22"/>
+  <dimension ref="A1:I40"/>
   <sheetFormatPr defaultColWidth="8.6796875" defaultRowHeight="15" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
   <cols>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1" min="1" style="0" width="30"/>
@@ -2272,20 +2353,22 @@
         <v>87</v>
       </c>
       <c r="C5" s="13" t="n">
-        <v>1</v>
-      </c>
-      <c r="D5" s="11"/>
-      <c r="E5" s="11"/>
-      <c r="F5" s="15" t="str">
+        <v>3000000</v>
+      </c>
+      <c r="D5" s="11" t="n">
+        <v>51000000</v>
+      </c>
+      <c r="E5" s="11" t="n">
+        <v>39000000</v>
+      </c>
+      <c r="F5" s="15" t="n">
         <f aca="false">IF(ISNUMBER(D5),MAX(0,D5-N(E5)),"")</f>
-        <v/>
-      </c>
-      <c r="G5" s="11" t="n">
-        <v>12860000</v>
-      </c>
+        <v>12000000</v>
+      </c>
+      <c r="G5" s="11"/>
       <c r="H5" s="15" t="n">
         <f aca="false">IF(ISNUMBER(D5),MIN(N(G5)*N(C5),N(F5)),N(G5)*N(C5))</f>
-        <v>12860000</v>
+        <v>0</v>
       </c>
       <c r="I5" s="16" t="s">
         <v>88</v>
@@ -2293,44 +2376,54 @@
     </row>
     <row r="6" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A6" s="12" t="s">
-        <v>86</v>
+        <v>89</v>
       </c>
       <c r="B6" s="12" t="s">
-        <v>89</v>
+        <v>90</v>
       </c>
       <c r="C6" s="13" t="n">
-        <v>1000</v>
-      </c>
-      <c r="D6" s="11"/>
-      <c r="E6" s="11"/>
-      <c r="F6" s="15" t="str">
+        <v>1</v>
+      </c>
+      <c r="D6" s="11" t="n">
+        <v>500000000</v>
+      </c>
+      <c r="E6" s="11" t="n">
+        <v>153625315</v>
+      </c>
+      <c r="F6" s="15" t="n">
         <f aca="false">IF(ISNUMBER(D6),MAX(0,D6-N(E6)),"")</f>
-        <v/>
-      </c>
-      <c r="G6" s="11"/>
+        <v>346374685</v>
+      </c>
+      <c r="G6" s="11" t="n">
+        <v>12860000</v>
+      </c>
       <c r="H6" s="15" t="n">
         <f aca="false">IF(ISNUMBER(D6),MIN(N(G6)*N(C6),N(F6)),N(G6)*N(C6))</f>
-        <v>0</v>
+        <v>12860000</v>
       </c>
       <c r="I6" s="16" t="s">
-        <v>90</v>
+        <v>91</v>
       </c>
     </row>
     <row r="7" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A7" s="12" t="s">
-        <v>86</v>
+        <v>89</v>
       </c>
       <c r="B7" s="12" t="s">
-        <v>91</v>
+        <v>92</v>
       </c>
       <c r="C7" s="13" t="n">
-        <v>5000</v>
-      </c>
-      <c r="D7" s="11"/>
-      <c r="E7" s="11"/>
-      <c r="F7" s="15" t="str">
+        <v>1000</v>
+      </c>
+      <c r="D7" s="11" t="n">
+        <v>250000000</v>
+      </c>
+      <c r="E7" s="11" t="n">
+        <v>10300000</v>
+      </c>
+      <c r="F7" s="15" t="n">
         <f aca="false">IF(ISNUMBER(D7),MAX(0,D7-N(E7)),"")</f>
-        <v/>
+        <v>239700000</v>
       </c>
       <c r="G7" s="11"/>
       <c r="H7" s="15" t="n">
@@ -2338,99 +2431,127 @@
         <v>0</v>
       </c>
       <c r="I7" s="16" t="s">
-        <v>92</v>
+        <v>93</v>
       </c>
     </row>
     <row r="8" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A8" s="12" t="s">
-        <v>86</v>
+        <v>89</v>
       </c>
       <c r="B8" s="12" t="s">
-        <v>93</v>
+        <v>94</v>
       </c>
       <c r="C8" s="13" t="n">
-        <v>1</v>
-      </c>
-      <c r="D8" s="11"/>
-      <c r="E8" s="11"/>
-      <c r="F8" s="15" t="str">
+        <v>5000</v>
+      </c>
+      <c r="D8" s="11" t="n">
+        <v>500000000</v>
+      </c>
+      <c r="E8" s="11" t="n">
+        <v>58180000</v>
+      </c>
+      <c r="F8" s="15" t="n">
         <f aca="false">IF(ISNUMBER(D8),MAX(0,D8-N(E8)),"")</f>
-        <v/>
+        <v>441820000</v>
       </c>
       <c r="G8" s="11"/>
       <c r="H8" s="15" t="n">
         <f aca="false">IF(ISNUMBER(D8),MIN(N(G8)*N(C8),N(F8)),N(G8)*N(C8))</f>
         <v>0</v>
       </c>
-      <c r="I8" s="16" t="s">
-        <v>94</v>
-      </c>
+      <c r="I8" s="16"/>
     </row>
     <row r="9" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A9" s="12" t="s">
-        <v>86</v>
+        <v>95</v>
       </c>
       <c r="B9" s="12" t="s">
-        <v>95</v>
-      </c>
-      <c r="C9" s="11"/>
-      <c r="D9" s="11"/>
-      <c r="E9" s="11"/>
-      <c r="F9" s="15" t="str">
+        <v>96</v>
+      </c>
+      <c r="C9" s="13" t="n">
+        <v>1</v>
+      </c>
+      <c r="D9" s="11" t="n">
+        <v>88000000</v>
+      </c>
+      <c r="E9" s="11" t="n">
+        <v>11025000</v>
+      </c>
+      <c r="F9" s="15" t="n">
         <f aca="false">IF(ISNUMBER(D9),MAX(0,D9-N(E9)),"")</f>
-        <v/>
+        <v>76975000</v>
       </c>
       <c r="G9" s="11"/>
       <c r="H9" s="15" t="n">
         <f aca="false">IF(ISNUMBER(D9),MIN(N(G9)*N(C9),N(F9)),N(G9)*N(C9))</f>
         <v>0</v>
       </c>
-      <c r="I9" s="16" t="s">
-        <v>96</v>
-      </c>
+      <c r="I9" s="16"/>
     </row>
     <row r="10" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A10" s="12"/>
-      <c r="B10" s="12"/>
-      <c r="C10" s="11"/>
-      <c r="D10" s="11"/>
-      <c r="E10" s="11"/>
-      <c r="F10" s="15" t="str">
+      <c r="A10" s="12" t="s">
+        <v>95</v>
+      </c>
+      <c r="B10" s="12" t="s">
+        <v>97</v>
+      </c>
+      <c r="C10" s="13" t="n">
+        <v>1</v>
+      </c>
+      <c r="D10" s="11" t="n">
+        <v>50000000</v>
+      </c>
+      <c r="E10" s="11" t="n">
+        <v>7400000</v>
+      </c>
+      <c r="F10" s="15" t="n">
         <f aca="false">IF(ISNUMBER(D10),MAX(0,D10-N(E10)),"")</f>
-        <v/>
+        <v>42600000</v>
       </c>
       <c r="G10" s="11"/>
       <c r="H10" s="15" t="n">
         <f aca="false">IF(ISNUMBER(D10),MIN(N(G10)*N(C10),N(F10)),N(G10)*N(C10))</f>
         <v>0</v>
       </c>
-      <c r="I10" s="16" t="s">
-        <v>97</v>
-      </c>
+      <c r="I10" s="16"/>
     </row>
     <row r="11" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A11" s="12"/>
-      <c r="B11" s="12"/>
-      <c r="C11" s="11"/>
-      <c r="D11" s="11"/>
-      <c r="E11" s="11"/>
-      <c r="F11" s="15" t="str">
+      <c r="A11" s="12" t="s">
+        <v>95</v>
+      </c>
+      <c r="B11" s="12" t="s">
+        <v>98</v>
+      </c>
+      <c r="C11" s="13" t="n">
+        <v>1</v>
+      </c>
+      <c r="D11" s="11" t="n">
+        <v>50000000</v>
+      </c>
+      <c r="E11" s="11" t="n">
+        <v>7401500</v>
+      </c>
+      <c r="F11" s="15" t="n">
         <f aca="false">IF(ISNUMBER(D11),MAX(0,D11-N(E11)),"")</f>
-        <v/>
+        <v>42598500</v>
       </c>
       <c r="G11" s="11"/>
       <c r="H11" s="15" t="n">
         <f aca="false">IF(ISNUMBER(D11),MIN(N(G11)*N(C11),N(F11)),N(G11)*N(C11))</f>
         <v>0</v>
       </c>
-      <c r="I11" s="16" t="s">
-        <v>97</v>
-      </c>
+      <c r="I11" s="16"/>
     </row>
     <row r="12" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A12" s="12"/>
-      <c r="B12" s="12"/>
-      <c r="C12" s="11"/>
+      <c r="A12" s="12" t="s">
+        <v>95</v>
+      </c>
+      <c r="B12" s="12" t="s">
+        <v>99</v>
+      </c>
+      <c r="C12" s="13" t="n">
+        <v>1</v>
+      </c>
       <c r="D12" s="11"/>
       <c r="E12" s="11"/>
       <c r="F12" s="15" t="str">
@@ -2443,13 +2564,19 @@
         <v>0</v>
       </c>
       <c r="I12" s="16" t="s">
-        <v>97</v>
+        <v>100</v>
       </c>
     </row>
     <row r="13" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A13" s="12"/>
-      <c r="B13" s="12"/>
-      <c r="C13" s="11"/>
+      <c r="A13" s="12" t="s">
+        <v>95</v>
+      </c>
+      <c r="B13" s="12" t="s">
+        <v>101</v>
+      </c>
+      <c r="C13" s="13" t="n">
+        <v>1</v>
+      </c>
       <c r="D13" s="11"/>
       <c r="E13" s="11"/>
       <c r="F13" s="15" t="str">
@@ -2462,13 +2589,19 @@
         <v>0</v>
       </c>
       <c r="I13" s="16" t="s">
-        <v>97</v>
+        <v>100</v>
       </c>
     </row>
     <row r="14" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A14" s="12"/>
-      <c r="B14" s="12"/>
-      <c r="C14" s="11"/>
+      <c r="A14" s="12" t="s">
+        <v>95</v>
+      </c>
+      <c r="B14" s="12" t="s">
+        <v>102</v>
+      </c>
+      <c r="C14" s="13" t="n">
+        <v>1</v>
+      </c>
       <c r="D14" s="11"/>
       <c r="E14" s="11"/>
       <c r="F14" s="15" t="str">
@@ -2481,57 +2614,513 @@
         <v>0</v>
       </c>
       <c r="I14" s="16" t="s">
-        <v>97</v>
+        <v>100</v>
+      </c>
+    </row>
+    <row r="15" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A15" s="12" t="s">
+        <v>95</v>
+      </c>
+      <c r="B15" s="12" t="s">
+        <v>103</v>
+      </c>
+      <c r="C15" s="13" t="n">
+        <v>1</v>
+      </c>
+      <c r="D15" s="11"/>
+      <c r="E15" s="11"/>
+      <c r="F15" s="15" t="str">
+        <f aca="false">IF(ISNUMBER(D15),MAX(0,D15-N(E15)),"")</f>
+        <v/>
+      </c>
+      <c r="G15" s="11"/>
+      <c r="H15" s="15" t="n">
+        <f aca="false">IF(ISNUMBER(D15),MIN(N(G15)*N(C15),N(F15)),N(G15)*N(C15))</f>
+        <v>0</v>
+      </c>
+      <c r="I15" s="16" t="s">
+        <v>100</v>
       </c>
     </row>
     <row r="16" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A16" s="3" t="s">
+      <c r="A16" s="12" t="s">
+        <v>104</v>
+      </c>
+      <c r="B16" s="12" t="s">
+        <v>105</v>
+      </c>
+      <c r="C16" s="13" t="n">
+        <v>2000000</v>
+      </c>
+      <c r="D16" s="11" t="n">
+        <v>6000000</v>
+      </c>
+      <c r="E16" s="11" t="n">
+        <v>6000000</v>
+      </c>
+      <c r="F16" s="15" t="n">
+        <f aca="false">IF(ISNUMBER(D16),MAX(0,D16-N(E16)),"")</f>
+        <v>0</v>
+      </c>
+      <c r="G16" s="11"/>
+      <c r="H16" s="15" t="n">
+        <f aca="false">IF(ISNUMBER(D16),MIN(N(G16)*N(C16),N(F16)),N(G16)*N(C16))</f>
+        <v>0</v>
+      </c>
+      <c r="I16" s="16" t="s">
+        <v>106</v>
+      </c>
+    </row>
+    <row r="17" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A17" s="12" t="s">
+        <v>104</v>
+      </c>
+      <c r="B17" s="12" t="s">
+        <v>107</v>
+      </c>
+      <c r="C17" s="13" t="n">
+        <v>3000000</v>
+      </c>
+      <c r="D17" s="11" t="n">
+        <v>9000000</v>
+      </c>
+      <c r="E17" s="11" t="n">
+        <v>6000000</v>
+      </c>
+      <c r="F17" s="15" t="n">
+        <f aca="false">IF(ISNUMBER(D17),MAX(0,D17-N(E17)),"")</f>
+        <v>3000000</v>
+      </c>
+      <c r="G17" s="11"/>
+      <c r="H17" s="15" t="n">
+        <f aca="false">IF(ISNUMBER(D17),MIN(N(G17)*N(C17),N(F17)),N(G17)*N(C17))</f>
+        <v>0</v>
+      </c>
+      <c r="I17" s="16" t="s">
+        <v>106</v>
+      </c>
+    </row>
+    <row r="18" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A18" s="12" t="s">
+        <v>104</v>
+      </c>
+      <c r="B18" s="12" t="s">
+        <v>108</v>
+      </c>
+      <c r="C18" s="13" t="n">
+        <v>2000000</v>
+      </c>
+      <c r="D18" s="11" t="n">
+        <v>10000000</v>
+      </c>
+      <c r="E18" s="11" t="n">
+        <v>10000000</v>
+      </c>
+      <c r="F18" s="15" t="n">
+        <f aca="false">IF(ISNUMBER(D18),MAX(0,D18-N(E18)),"")</f>
+        <v>0</v>
+      </c>
+      <c r="G18" s="11"/>
+      <c r="H18" s="15" t="n">
+        <f aca="false">IF(ISNUMBER(D18),MIN(N(G18)*N(C18),N(F18)),N(G18)*N(C18))</f>
+        <v>0</v>
+      </c>
+      <c r="I18" s="16" t="s">
+        <v>106</v>
+      </c>
+    </row>
+    <row r="19" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A19" s="12" t="s">
+        <v>104</v>
+      </c>
+      <c r="B19" s="12" t="s">
+        <v>109</v>
+      </c>
+      <c r="C19" s="13" t="n">
+        <v>3000000</v>
+      </c>
+      <c r="D19" s="11" t="n">
+        <v>15000000</v>
+      </c>
+      <c r="E19" s="11" t="n">
+        <v>0</v>
+      </c>
+      <c r="F19" s="15" t="n">
+        <f aca="false">IF(ISNUMBER(D19),MAX(0,D19-N(E19)),"")</f>
+        <v>15000000</v>
+      </c>
+      <c r="G19" s="11"/>
+      <c r="H19" s="15" t="n">
+        <f aca="false">IF(ISNUMBER(D19),MIN(N(G19)*N(C19),N(F19)),N(G19)*N(C19))</f>
+        <v>0</v>
+      </c>
+      <c r="I19" s="16" t="s">
+        <v>106</v>
+      </c>
+    </row>
+    <row r="20" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A20" s="12" t="s">
+        <v>104</v>
+      </c>
+      <c r="B20" s="12" t="s">
+        <v>110</v>
+      </c>
+      <c r="C20" s="13" t="n">
+        <v>2000000</v>
+      </c>
+      <c r="D20" s="11" t="n">
+        <v>10000000</v>
+      </c>
+      <c r="E20" s="11" t="n">
+        <v>10000000</v>
+      </c>
+      <c r="F20" s="15" t="n">
+        <f aca="false">IF(ISNUMBER(D20),MAX(0,D20-N(E20)),"")</f>
+        <v>0</v>
+      </c>
+      <c r="G20" s="11"/>
+      <c r="H20" s="15" t="n">
+        <f aca="false">IF(ISNUMBER(D20),MIN(N(G20)*N(C20),N(F20)),N(G20)*N(C20))</f>
+        <v>0</v>
+      </c>
+      <c r="I20" s="16" t="s">
+        <v>106</v>
+      </c>
+    </row>
+    <row r="21" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A21" s="12" t="s">
+        <v>104</v>
+      </c>
+      <c r="B21" s="12" t="s">
+        <v>111</v>
+      </c>
+      <c r="C21" s="13" t="n">
+        <v>3000000</v>
+      </c>
+      <c r="D21" s="11" t="n">
+        <v>15000000</v>
+      </c>
+      <c r="E21" s="11" t="n">
+        <v>15000000</v>
+      </c>
+      <c r="F21" s="15" t="n">
+        <f aca="false">IF(ISNUMBER(D21),MAX(0,D21-N(E21)),"")</f>
+        <v>0</v>
+      </c>
+      <c r="G21" s="11"/>
+      <c r="H21" s="15" t="n">
+        <f aca="false">IF(ISNUMBER(D21),MIN(N(G21)*N(C21),N(F21)),N(G21)*N(C21))</f>
+        <v>0</v>
+      </c>
+      <c r="I21" s="16" t="s">
+        <v>106</v>
+      </c>
+    </row>
+    <row r="22" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A22" s="12" t="s">
+        <v>104</v>
+      </c>
+      <c r="B22" s="12" t="s">
+        <v>112</v>
+      </c>
+      <c r="C22" s="13" t="n">
+        <v>5000000</v>
+      </c>
+      <c r="D22" s="11" t="n">
+        <v>25000000</v>
+      </c>
+      <c r="E22" s="11" t="n">
+        <v>20000000</v>
+      </c>
+      <c r="F22" s="15" t="n">
+        <f aca="false">IF(ISNUMBER(D22),MAX(0,D22-N(E22)),"")</f>
+        <v>5000000</v>
+      </c>
+      <c r="G22" s="11" t="n">
+        <v>1</v>
+      </c>
+      <c r="H22" s="15" t="n">
+        <f aca="false">IF(ISNUMBER(D22),MIN(N(G22)*N(C22),N(F22)),N(G22)*N(C22))</f>
+        <v>5000000</v>
+      </c>
+      <c r="I22" s="16" t="s">
+        <v>113</v>
+      </c>
+    </row>
+    <row r="23" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A23" s="12" t="s">
+        <v>104</v>
+      </c>
+      <c r="B23" s="12" t="s">
+        <v>114</v>
+      </c>
+      <c r="C23" s="13" t="n">
+        <v>5000000</v>
+      </c>
+      <c r="D23" s="11" t="n">
+        <v>25000000</v>
+      </c>
+      <c r="E23" s="11" t="n">
+        <v>15000000</v>
+      </c>
+      <c r="F23" s="15" t="n">
+        <f aca="false">IF(ISNUMBER(D23),MAX(0,D23-N(E23)),"")</f>
+        <v>10000000</v>
+      </c>
+      <c r="G23" s="11"/>
+      <c r="H23" s="15" t="n">
+        <f aca="false">IF(ISNUMBER(D23),MIN(N(G23)*N(C23),N(F23)),N(G23)*N(C23))</f>
+        <v>0</v>
+      </c>
+      <c r="I23" s="16" t="s">
+        <v>106</v>
+      </c>
+    </row>
+    <row r="24" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A24" s="12" t="s">
+        <v>104</v>
+      </c>
+      <c r="B24" s="12" t="s">
+        <v>115</v>
+      </c>
+      <c r="C24" s="13" t="n">
+        <v>5000000</v>
+      </c>
+      <c r="D24" s="11" t="n">
+        <v>25000000</v>
+      </c>
+      <c r="E24" s="11" t="n">
+        <v>25000000</v>
+      </c>
+      <c r="F24" s="15" t="n">
+        <f aca="false">IF(ISNUMBER(D24),MAX(0,D24-N(E24)),"")</f>
+        <v>0</v>
+      </c>
+      <c r="G24" s="11"/>
+      <c r="H24" s="15" t="n">
+        <f aca="false">IF(ISNUMBER(D24),MIN(N(G24)*N(C24),N(F24)),N(G24)*N(C24))</f>
+        <v>0</v>
+      </c>
+      <c r="I24" s="16" t="s">
+        <v>106</v>
+      </c>
+    </row>
+    <row r="25" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A25" s="12" t="s">
+        <v>104</v>
+      </c>
+      <c r="B25" s="12" t="s">
+        <v>116</v>
+      </c>
+      <c r="C25" s="13" t="n">
+        <v>8000000</v>
+      </c>
+      <c r="D25" s="11" t="n">
+        <v>40000000</v>
+      </c>
+      <c r="E25" s="11" t="n">
+        <v>0</v>
+      </c>
+      <c r="F25" s="15" t="n">
+        <f aca="false">IF(ISNUMBER(D25),MAX(0,D25-N(E25)),"")</f>
+        <v>40000000</v>
+      </c>
+      <c r="G25" s="11"/>
+      <c r="H25" s="15" t="n">
+        <f aca="false">IF(ISNUMBER(D25),MIN(N(G25)*N(C25),N(F25)),N(G25)*N(C25))</f>
+        <v>0</v>
+      </c>
+      <c r="I25" s="16" t="s">
+        <v>106</v>
+      </c>
+    </row>
+    <row r="26" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A26" s="12" t="s">
+        <v>104</v>
+      </c>
+      <c r="B26" s="12" t="s">
+        <v>117</v>
+      </c>
+      <c r="C26" s="13" t="n">
+        <v>8000000</v>
+      </c>
+      <c r="D26" s="11" t="n">
+        <v>40000000</v>
+      </c>
+      <c r="E26" s="11" t="n">
+        <v>0</v>
+      </c>
+      <c r="F26" s="15" t="n">
+        <f aca="false">IF(ISNUMBER(D26),MAX(0,D26-N(E26)),"")</f>
+        <v>40000000</v>
+      </c>
+      <c r="G26" s="11"/>
+      <c r="H26" s="15" t="n">
+        <f aca="false">IF(ISNUMBER(D26),MIN(N(G26)*N(C26),N(F26)),N(G26)*N(C26))</f>
+        <v>0</v>
+      </c>
+      <c r="I26" s="16" t="s">
+        <v>106</v>
+      </c>
+    </row>
+    <row r="27" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A27" s="12" t="s">
+        <v>104</v>
+      </c>
+      <c r="B27" s="12" t="s">
+        <v>118</v>
+      </c>
+      <c r="C27" s="13" t="n">
+        <v>8000000</v>
+      </c>
+      <c r="D27" s="11" t="n">
+        <v>40000000</v>
+      </c>
+      <c r="E27" s="11" t="n">
+        <v>0</v>
+      </c>
+      <c r="F27" s="15" t="n">
+        <f aca="false">IF(ISNUMBER(D27),MAX(0,D27-N(E27)),"")</f>
+        <v>40000000</v>
+      </c>
+      <c r="G27" s="11"/>
+      <c r="H27" s="15" t="n">
+        <f aca="false">IF(ISNUMBER(D27),MIN(N(G27)*N(C27),N(F27)),N(G27)*N(C27))</f>
+        <v>0</v>
+      </c>
+      <c r="I27" s="16" t="s">
+        <v>106</v>
+      </c>
+    </row>
+    <row r="28" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A28" s="12" t="s">
+        <v>119</v>
+      </c>
+      <c r="B28" s="12" t="s">
+        <v>120</v>
+      </c>
+      <c r="C28" s="13" t="n">
+        <v>1</v>
+      </c>
+      <c r="D28" s="11"/>
+      <c r="E28" s="11"/>
+      <c r="F28" s="15" t="str">
+        <f aca="false">IF(ISNUMBER(D28),MAX(0,D28-N(E28)),"")</f>
+        <v/>
+      </c>
+      <c r="G28" s="11"/>
+      <c r="H28" s="15" t="n">
+        <f aca="false">IF(ISNUMBER(D28),MIN(N(G28)*N(C28),N(F28)),N(G28)*N(C28))</f>
+        <v>0</v>
+      </c>
+      <c r="I28" s="16" t="s">
+        <v>121</v>
+      </c>
+    </row>
+    <row r="29" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A29" s="12"/>
+      <c r="B29" s="12"/>
+      <c r="C29" s="11"/>
+      <c r="D29" s="11"/>
+      <c r="E29" s="11"/>
+      <c r="F29" s="15" t="str">
+        <f aca="false">IF(ISNUMBER(D29),MAX(0,D29-N(E29)),"")</f>
+        <v/>
+      </c>
+      <c r="G29" s="11"/>
+      <c r="H29" s="15" t="n">
+        <f aca="false">IF(ISNUMBER(D29),MIN(N(G29)*N(C29),N(F29)),N(G29)*N(C29))</f>
+        <v>0</v>
+      </c>
+      <c r="I29" s="16" t="s">
+        <v>122</v>
+      </c>
+    </row>
+    <row r="30" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A30" s="12"/>
+      <c r="B30" s="12"/>
+      <c r="C30" s="11"/>
+      <c r="D30" s="11"/>
+      <c r="E30" s="11"/>
+      <c r="F30" s="15" t="str">
+        <f aca="false">IF(ISNUMBER(D30),MAX(0,D30-N(E30)),"")</f>
+        <v/>
+      </c>
+      <c r="G30" s="11"/>
+      <c r="H30" s="15" t="n">
+        <f aca="false">IF(ISNUMBER(D30),MIN(N(G30)*N(C30),N(F30)),N(G30)*N(C30))</f>
+        <v>0</v>
+      </c>
+      <c r="I30" s="16" t="s">
+        <v>122</v>
+      </c>
+    </row>
+    <row r="32" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A32" s="3" t="s">
+        <v>123</v>
+      </c>
+      <c r="B32" s="7" t="n">
+        <f aca="false">SUM(E5:E30)</f>
+        <v>393931815</v>
+      </c>
+    </row>
+    <row r="33" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A33" s="3" t="s">
+        <v>124</v>
+      </c>
+      <c r="B33" s="7" t="n">
+        <f aca="false">'Iso Fest'!B6-B32</f>
+        <v>85404500</v>
+      </c>
+    </row>
+    <row r="34" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A34" s="3" t="s">
         <v>9</v>
       </c>
-      <c r="B16" s="7" t="n">
+      <c r="B34" s="7" t="n">
         <f aca="false">'Iso Fest'!B6</f>
         <v>479336315</v>
       </c>
     </row>
-    <row r="17" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A17" s="3" t="s">
-        <v>98</v>
-      </c>
-      <c r="B17" s="7" t="n">
-        <f aca="false">SUM(H5:H14)</f>
-        <v>12860000</v>
-      </c>
-    </row>
-    <row r="18" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A18" s="3" t="s">
-        <v>99</v>
-      </c>
-      <c r="B18" s="7" t="n">
-        <f aca="false">B16+B17</f>
-        <v>492196315</v>
-      </c>
-    </row>
-    <row r="19" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A19" s="3" t="s">
-        <v>100</v>
-      </c>
-      <c r="B19" s="7" t="n">
-        <f aca="false">IFERROR(INDEX('Iso Fest'!A13:A54,MATCH(B18,'Iso Fest'!B13:B54,1)),"Below milestone 15")</f>
+    <row r="35" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A35" s="3" t="s">
+        <v>125</v>
+      </c>
+      <c r="B35" s="7" t="n">
+        <f aca="false">SUM(H5:H30)</f>
+        <v>17860000</v>
+      </c>
+    </row>
+    <row r="36" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A36" s="3" t="s">
+        <v>126</v>
+      </c>
+      <c r="B36" s="7" t="n">
+        <f aca="false">B34+B35</f>
+        <v>497196315</v>
+      </c>
+    </row>
+    <row r="37" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A37" s="3" t="s">
+        <v>127</v>
+      </c>
+      <c r="B37" s="7" t="n">
+        <f aca="false">IFERROR(INDEX('Iso Fest'!A13:A54,MATCH(B36,'Iso Fest'!B13:B54,1)),"Below milestone 15")</f>
         <v>22</v>
       </c>
     </row>
-    <row r="20" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A20" s="3" t="s">
-        <v>101</v>
-      </c>
-      <c r="B20" s="7" t="n">
-        <f aca="false">MAX(0,INDEX('Iso Fest'!B13:B54,'Iso Fest'!B9)-B18)</f>
-        <v>107803685</v>
-      </c>
-    </row>
-    <row r="22" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A22" s="2" t="s">
-        <v>102</v>
+    <row r="38" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A38" s="3" t="s">
+        <v>128</v>
+      </c>
+      <c r="B38" s="7" t="n">
+        <f aca="false">MAX(0,INDEX('Iso Fest'!B13:B54,'Iso Fest'!B9)-B36)</f>
+        <v>102803685</v>
+      </c>
+    </row>
+    <row r="40" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A40" s="2" t="s">
+        <v>129</v>
       </c>
     </row>
   </sheetData>

--- a/Iso_Fest_Tracker.xlsx
+++ b/Iso_Fest_Tracker.xlsx
@@ -960,7 +960,7 @@
         <v>9</v>
       </c>
       <c r="B6" s="6" t="n">
-        <v>479336315</v>
+        <v>482927315</v>
       </c>
       <c r="D6" s="4" t="s">
         <v>10</v>
@@ -1008,7 +1008,7 @@
       </c>
       <c r="B8" s="7" t="n">
         <f aca="false">IFERROR(INDEX(I13:I54,MATCH(TRUE(),INDEX(B13:B54&gt;B6,0),0)),0)</f>
-        <v>20663685</v>
+        <v>17072685</v>
       </c>
     </row>
     <row r="9" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -1023,7 +1023,7 @@
       </c>
       <c r="G9" s="7" t="n">
         <f aca="false">Scoring!B36</f>
-        <v>497196315</v>
+        <v>500787315</v>
       </c>
     </row>
     <row r="10" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -1032,14 +1032,14 @@
       </c>
       <c r="B10" s="7" t="n">
         <f aca="false">MAX(0,INDEX(B13:B54,B9)-B6)</f>
-        <v>120663685</v>
+        <v>117072685</v>
       </c>
       <c r="D10" s="3" t="s">
         <v>17</v>
       </c>
       <c r="G10" s="7" t="n">
         <f aca="false">Scoring!B37</f>
-        <v>22</v>
+        <v>23</v>
       </c>
     </row>
     <row r="11" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -1048,7 +1048,7 @@
       </c>
       <c r="B11" s="7" t="n">
         <f aca="true">IFERROR(B10/MAX(B5-NOW(),0.01),0)</f>
-        <v>28138403.026481</v>
+        <v>27343380.829674</v>
       </c>
     </row>
     <row r="12" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -1717,7 +1717,7 @@
       </c>
       <c r="I35" s="15" t="n">
         <f aca="false">IF(B35="","",MAX(0,B35-$B$6))</f>
-        <v>20663685</v>
+        <v>17072685</v>
       </c>
     </row>
     <row r="36" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -1745,7 +1745,7 @@
       </c>
       <c r="I36" s="15" t="n">
         <f aca="false">IF(B36="","",MAX(0,B36-$B$6))</f>
-        <v>45663685</v>
+        <v>42072685</v>
       </c>
     </row>
     <row r="37" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -1775,7 +1775,7 @@
       </c>
       <c r="I37" s="15" t="n">
         <f aca="false">IF(B37="","",MAX(0,B37-$B$6))</f>
-        <v>70663685</v>
+        <v>67072685</v>
       </c>
     </row>
     <row r="38" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -1803,7 +1803,7 @@
       </c>
       <c r="I38" s="15" t="n">
         <f aca="false">IF(B38="","",MAX(0,B38-$B$6))</f>
-        <v>120663685</v>
+        <v>117072685</v>
       </c>
     </row>
     <row r="39" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -1833,7 +1833,7 @@
       </c>
       <c r="I39" s="15" t="n">
         <f aca="false">IF(B39="","",MAX(0,B39-$B$6))</f>
-        <v>170663685</v>
+        <v>167072685</v>
       </c>
     </row>
     <row r="40" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -1861,7 +1861,7 @@
       </c>
       <c r="I40" s="15" t="n">
         <f aca="false">IF(B40="","",MAX(0,B40-$B$6))</f>
-        <v>270663685</v>
+        <v>267072685</v>
       </c>
     </row>
     <row r="41" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -1891,7 +1891,7 @@
       </c>
       <c r="I41" s="15" t="n">
         <f aca="false">IF(B41="","",MAX(0,B41-$B$6))</f>
-        <v>420663685</v>
+        <v>417072685</v>
       </c>
     </row>
     <row r="42" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -1919,7 +1919,7 @@
       </c>
       <c r="I42" s="15" t="n">
         <f aca="false">IF(B42="","",MAX(0,B42-$B$6))</f>
-        <v>620663685</v>
+        <v>617072685</v>
       </c>
     </row>
     <row r="43" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -1949,7 +1949,7 @@
       </c>
       <c r="I43" s="15" t="n">
         <f aca="false">IF(B43="","",MAX(0,B43-$B$6))</f>
-        <v>820663685</v>
+        <v>817072685</v>
       </c>
     </row>
     <row r="44" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -1977,7 +1977,7 @@
       </c>
       <c r="I44" s="15" t="n">
         <f aca="false">IF(B44="","",MAX(0,B44-$B$6))</f>
-        <v>1020663685</v>
+        <v>1017072685</v>
       </c>
     </row>
     <row r="45" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -2005,7 +2005,7 @@
       </c>
       <c r="I45" s="15" t="n">
         <f aca="false">IF(B45="","",MAX(0,B45-$B$6))</f>
-        <v>1220663685</v>
+        <v>1217072685</v>
       </c>
     </row>
     <row r="46" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -2033,7 +2033,7 @@
       </c>
       <c r="I46" s="15" t="n">
         <f aca="false">IF(B46="","",MAX(0,B46-$B$6))</f>
-        <v>1420663685</v>
+        <v>1417072685</v>
       </c>
     </row>
     <row r="47" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -2061,7 +2061,7 @@
       </c>
       <c r="I47" s="15" t="n">
         <f aca="false">IF(B47="","",MAX(0,B47-$B$6))</f>
-        <v>1620663685</v>
+        <v>1617072685</v>
       </c>
     </row>
     <row r="48" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -2089,7 +2089,7 @@
       </c>
       <c r="I48" s="15" t="n">
         <f aca="false">IF(B48="","",MAX(0,B48-$B$6))</f>
-        <v>1820663685</v>
+        <v>1817072685</v>
       </c>
     </row>
     <row r="49" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -2117,7 +2117,7 @@
       </c>
       <c r="I49" s="15" t="n">
         <f aca="false">IF(B49="","",MAX(0,B49-$B$6))</f>
-        <v>2020663685</v>
+        <v>2017072685</v>
       </c>
     </row>
     <row r="50" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -2145,7 +2145,7 @@
       </c>
       <c r="I50" s="15" t="n">
         <f aca="false">IF(B50="","",MAX(0,B50-$B$6))</f>
-        <v>2220663685</v>
+        <v>2217072685</v>
       </c>
     </row>
     <row r="51" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -2173,7 +2173,7 @@
       </c>
       <c r="I51" s="15" t="n">
         <f aca="false">IF(B51="","",MAX(0,B51-$B$6))</f>
-        <v>2420663685</v>
+        <v>2417072685</v>
       </c>
     </row>
     <row r="52" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -2201,7 +2201,7 @@
       </c>
       <c r="I52" s="15" t="n">
         <f aca="false">IF(B52="","",MAX(0,B52-$B$6))</f>
-        <v>2620663685</v>
+        <v>2617072685</v>
       </c>
     </row>
     <row r="53" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -2229,7 +2229,7 @@
       </c>
       <c r="I53" s="15" t="n">
         <f aca="false">IF(B53="","",MAX(0,B53-$B$6))</f>
-        <v>2820663685</v>
+        <v>2817072685</v>
       </c>
     </row>
     <row r="54" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -2257,7 +2257,7 @@
       </c>
       <c r="I54" s="15" t="n">
         <f aca="false">IF(B54="","",MAX(0,B54-$B$6))</f>
-        <v>3020663685</v>
+        <v>3017072685</v>
       </c>
     </row>
     <row r="56" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -3070,7 +3070,7 @@
       </c>
       <c r="B33" s="7" t="n">
         <f aca="false">'Iso Fest'!B6-B32</f>
-        <v>85404500</v>
+        <v>88995500</v>
       </c>
     </row>
     <row r="34" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -3079,7 +3079,7 @@
       </c>
       <c r="B34" s="7" t="n">
         <f aca="false">'Iso Fest'!B6</f>
-        <v>479336315</v>
+        <v>482927315</v>
       </c>
     </row>
     <row r="35" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -3097,7 +3097,7 @@
       </c>
       <c r="B36" s="7" t="n">
         <f aca="false">B34+B35</f>
-        <v>497196315</v>
+        <v>500787315</v>
       </c>
     </row>
     <row r="37" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -3106,7 +3106,7 @@
       </c>
       <c r="B37" s="7" t="n">
         <f aca="false">IFERROR(INDEX('Iso Fest'!A13:A54,MATCH(B36,'Iso Fest'!B13:B54,1)),"Below milestone 15")</f>
-        <v>22</v>
+        <v>23</v>
       </c>
     </row>
     <row r="38" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -3115,7 +3115,7 @@
       </c>
       <c r="B38" s="7" t="n">
         <f aca="false">MAX(0,INDEX('Iso Fest'!B13:B54,'Iso Fest'!B9)-B36)</f>
-        <v>102803685</v>
+        <v>99212685</v>
       </c>
     </row>
     <row r="40" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">

--- a/Iso_Fest_Tracker.xlsx
+++ b/Iso_Fest_Tracker.xlsx
@@ -960,7 +960,7 @@
         <v>9</v>
       </c>
       <c r="B6" s="6" t="n">
-        <v>482927315</v>
+        <v>483077315</v>
       </c>
       <c r="D6" s="4" t="s">
         <v>10</v>
@@ -1008,7 +1008,7 @@
       </c>
       <c r="B8" s="7" t="n">
         <f aca="false">IFERROR(INDEX(I13:I54,MATCH(TRUE(),INDEX(B13:B54&gt;B6,0),0)),0)</f>
-        <v>17072685</v>
+        <v>16922685</v>
       </c>
     </row>
     <row r="9" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -1023,7 +1023,7 @@
       </c>
       <c r="G9" s="7" t="n">
         <f aca="false">Scoring!B36</f>
-        <v>500787315</v>
+        <v>500937315</v>
       </c>
     </row>
     <row r="10" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -1032,7 +1032,7 @@
       </c>
       <c r="B10" s="7" t="n">
         <f aca="false">MAX(0,INDEX(B13:B54,B9)-B6)</f>
-        <v>117072685</v>
+        <v>116922685</v>
       </c>
       <c r="D10" s="3" t="s">
         <v>17</v>
@@ -1048,7 +1048,7 @@
       </c>
       <c r="B11" s="7" t="n">
         <f aca="true">IFERROR(B10/MAX(B5-NOW(),0.01),0)</f>
-        <v>27343380.829674</v>
+        <v>27547749.597424</v>
       </c>
     </row>
     <row r="12" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -1717,7 +1717,7 @@
       </c>
       <c r="I35" s="15" t="n">
         <f aca="false">IF(B35="","",MAX(0,B35-$B$6))</f>
-        <v>17072685</v>
+        <v>16922685</v>
       </c>
     </row>
     <row r="36" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -1745,7 +1745,7 @@
       </c>
       <c r="I36" s="15" t="n">
         <f aca="false">IF(B36="","",MAX(0,B36-$B$6))</f>
-        <v>42072685</v>
+        <v>41922685</v>
       </c>
     </row>
     <row r="37" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -1775,7 +1775,7 @@
       </c>
       <c r="I37" s="15" t="n">
         <f aca="false">IF(B37="","",MAX(0,B37-$B$6))</f>
-        <v>67072685</v>
+        <v>66922685</v>
       </c>
     </row>
     <row r="38" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -1803,7 +1803,7 @@
       </c>
       <c r="I38" s="15" t="n">
         <f aca="false">IF(B38="","",MAX(0,B38-$B$6))</f>
-        <v>117072685</v>
+        <v>116922685</v>
       </c>
     </row>
     <row r="39" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -1833,7 +1833,7 @@
       </c>
       <c r="I39" s="15" t="n">
         <f aca="false">IF(B39="","",MAX(0,B39-$B$6))</f>
-        <v>167072685</v>
+        <v>166922685</v>
       </c>
     </row>
     <row r="40" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -1861,7 +1861,7 @@
       </c>
       <c r="I40" s="15" t="n">
         <f aca="false">IF(B40="","",MAX(0,B40-$B$6))</f>
-        <v>267072685</v>
+        <v>266922685</v>
       </c>
     </row>
     <row r="41" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -1891,7 +1891,7 @@
       </c>
       <c r="I41" s="15" t="n">
         <f aca="false">IF(B41="","",MAX(0,B41-$B$6))</f>
-        <v>417072685</v>
+        <v>416922685</v>
       </c>
     </row>
     <row r="42" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -1919,7 +1919,7 @@
       </c>
       <c r="I42" s="15" t="n">
         <f aca="false">IF(B42="","",MAX(0,B42-$B$6))</f>
-        <v>617072685</v>
+        <v>616922685</v>
       </c>
     </row>
     <row r="43" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -1949,7 +1949,7 @@
       </c>
       <c r="I43" s="15" t="n">
         <f aca="false">IF(B43="","",MAX(0,B43-$B$6))</f>
-        <v>817072685</v>
+        <v>816922685</v>
       </c>
     </row>
     <row r="44" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -1977,7 +1977,7 @@
       </c>
       <c r="I44" s="15" t="n">
         <f aca="false">IF(B44="","",MAX(0,B44-$B$6))</f>
-        <v>1017072685</v>
+        <v>1016922685</v>
       </c>
     </row>
     <row r="45" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -2005,7 +2005,7 @@
       </c>
       <c r="I45" s="15" t="n">
         <f aca="false">IF(B45="","",MAX(0,B45-$B$6))</f>
-        <v>1217072685</v>
+        <v>1216922685</v>
       </c>
     </row>
     <row r="46" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -2033,7 +2033,7 @@
       </c>
       <c r="I46" s="15" t="n">
         <f aca="false">IF(B46="","",MAX(0,B46-$B$6))</f>
-        <v>1417072685</v>
+        <v>1416922685</v>
       </c>
     </row>
     <row r="47" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -2061,7 +2061,7 @@
       </c>
       <c r="I47" s="15" t="n">
         <f aca="false">IF(B47="","",MAX(0,B47-$B$6))</f>
-        <v>1617072685</v>
+        <v>1616922685</v>
       </c>
     </row>
     <row r="48" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -2089,7 +2089,7 @@
       </c>
       <c r="I48" s="15" t="n">
         <f aca="false">IF(B48="","",MAX(0,B48-$B$6))</f>
-        <v>1817072685</v>
+        <v>1816922685</v>
       </c>
     </row>
     <row r="49" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -2117,7 +2117,7 @@
       </c>
       <c r="I49" s="15" t="n">
         <f aca="false">IF(B49="","",MAX(0,B49-$B$6))</f>
-        <v>2017072685</v>
+        <v>2016922685</v>
       </c>
     </row>
     <row r="50" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -2145,7 +2145,7 @@
       </c>
       <c r="I50" s="15" t="n">
         <f aca="false">IF(B50="","",MAX(0,B50-$B$6))</f>
-        <v>2217072685</v>
+        <v>2216922685</v>
       </c>
     </row>
     <row r="51" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -2173,7 +2173,7 @@
       </c>
       <c r="I51" s="15" t="n">
         <f aca="false">IF(B51="","",MAX(0,B51-$B$6))</f>
-        <v>2417072685</v>
+        <v>2416922685</v>
       </c>
     </row>
     <row r="52" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -2201,7 +2201,7 @@
       </c>
       <c r="I52" s="15" t="n">
         <f aca="false">IF(B52="","",MAX(0,B52-$B$6))</f>
-        <v>2617072685</v>
+        <v>2616922685</v>
       </c>
     </row>
     <row r="53" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -2229,7 +2229,7 @@
       </c>
       <c r="I53" s="15" t="n">
         <f aca="false">IF(B53="","",MAX(0,B53-$B$6))</f>
-        <v>2817072685</v>
+        <v>2816922685</v>
       </c>
     </row>
     <row r="54" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -2257,7 +2257,7 @@
       </c>
       <c r="I54" s="15" t="n">
         <f aca="false">IF(B54="","",MAX(0,B54-$B$6))</f>
-        <v>3017072685</v>
+        <v>3016922685</v>
       </c>
     </row>
     <row r="56" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -2388,11 +2388,11 @@
         <v>500000000</v>
       </c>
       <c r="E6" s="11" t="n">
-        <v>153625315</v>
+        <v>153775315</v>
       </c>
       <c r="F6" s="15" t="n">
         <f aca="false">IF(ISNUMBER(D6),MAX(0,D6-N(E6)),"")</f>
-        <v>346374685</v>
+        <v>346224685</v>
       </c>
       <c r="G6" s="11" t="n">
         <v>12860000</v>
@@ -3061,7 +3061,7 @@
       </c>
       <c r="B32" s="7" t="n">
         <f aca="false">SUM(E5:E30)</f>
-        <v>393931815</v>
+        <v>394081815</v>
       </c>
     </row>
     <row r="33" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -3079,7 +3079,7 @@
       </c>
       <c r="B34" s="7" t="n">
         <f aca="false">'Iso Fest'!B6</f>
-        <v>482927315</v>
+        <v>483077315</v>
       </c>
     </row>
     <row r="35" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -3097,7 +3097,7 @@
       </c>
       <c r="B36" s="7" t="n">
         <f aca="false">B34+B35</f>
-        <v>500787315</v>
+        <v>500937315</v>
       </c>
     </row>
     <row r="37" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -3115,7 +3115,7 @@
       </c>
       <c r="B38" s="7" t="n">
         <f aca="false">MAX(0,INDEX('Iso Fest'!B13:B54,'Iso Fest'!B9)-B36)</f>
-        <v>99212685</v>
+        <v>99062685</v>
       </c>
     </row>
     <row r="40" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">

--- a/Iso_Fest_Tracker.xlsx
+++ b/Iso_Fest_Tracker.xlsx
@@ -960,7 +960,7 @@
         <v>9</v>
       </c>
       <c r="B6" s="6" t="n">
-        <v>483077315</v>
+        <v>487977315</v>
       </c>
       <c r="D6" s="4" t="s">
         <v>10</v>
@@ -1008,7 +1008,7 @@
       </c>
       <c r="B8" s="7" t="n">
         <f aca="false">IFERROR(INDEX(I13:I54,MATCH(TRUE(),INDEX(B13:B54&gt;B6,0),0)),0)</f>
-        <v>16922685</v>
+        <v>12022685</v>
       </c>
     </row>
     <row r="9" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -1023,7 +1023,7 @@
       </c>
       <c r="G9" s="7" t="n">
         <f aca="false">Scoring!B36</f>
-        <v>500937315</v>
+        <v>500667315</v>
       </c>
     </row>
     <row r="10" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -1032,7 +1032,7 @@
       </c>
       <c r="B10" s="7" t="n">
         <f aca="false">MAX(0,INDEX(B13:B54,B9)-B6)</f>
-        <v>116922685</v>
+        <v>112022685</v>
       </c>
       <c r="D10" s="3" t="s">
         <v>17</v>
@@ -1048,7 +1048,7 @@
       </c>
       <c r="B11" s="7" t="n">
         <f aca="true">IFERROR(B10/MAX(B5-NOW(),0.01),0)</f>
-        <v>27547749.597424</v>
+        <v>26416154.204047</v>
       </c>
     </row>
     <row r="12" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -1717,7 +1717,7 @@
       </c>
       <c r="I35" s="15" t="n">
         <f aca="false">IF(B35="","",MAX(0,B35-$B$6))</f>
-        <v>16922685</v>
+        <v>12022685</v>
       </c>
     </row>
     <row r="36" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -1745,7 +1745,7 @@
       </c>
       <c r="I36" s="15" t="n">
         <f aca="false">IF(B36="","",MAX(0,B36-$B$6))</f>
-        <v>41922685</v>
+        <v>37022685</v>
       </c>
     </row>
     <row r="37" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -1775,7 +1775,7 @@
       </c>
       <c r="I37" s="15" t="n">
         <f aca="false">IF(B37="","",MAX(0,B37-$B$6))</f>
-        <v>66922685</v>
+        <v>62022685</v>
       </c>
     </row>
     <row r="38" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -1803,7 +1803,7 @@
       </c>
       <c r="I38" s="15" t="n">
         <f aca="false">IF(B38="","",MAX(0,B38-$B$6))</f>
-        <v>116922685</v>
+        <v>112022685</v>
       </c>
     </row>
     <row r="39" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -1833,7 +1833,7 @@
       </c>
       <c r="I39" s="15" t="n">
         <f aca="false">IF(B39="","",MAX(0,B39-$B$6))</f>
-        <v>166922685</v>
+        <v>162022685</v>
       </c>
     </row>
     <row r="40" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -1861,7 +1861,7 @@
       </c>
       <c r="I40" s="15" t="n">
         <f aca="false">IF(B40="","",MAX(0,B40-$B$6))</f>
-        <v>266922685</v>
+        <v>262022685</v>
       </c>
     </row>
     <row r="41" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -1891,7 +1891,7 @@
       </c>
       <c r="I41" s="15" t="n">
         <f aca="false">IF(B41="","",MAX(0,B41-$B$6))</f>
-        <v>416922685</v>
+        <v>412022685</v>
       </c>
     </row>
     <row r="42" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -1919,7 +1919,7 @@
       </c>
       <c r="I42" s="15" t="n">
         <f aca="false">IF(B42="","",MAX(0,B42-$B$6))</f>
-        <v>616922685</v>
+        <v>612022685</v>
       </c>
     </row>
     <row r="43" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -1949,7 +1949,7 @@
       </c>
       <c r="I43" s="15" t="n">
         <f aca="false">IF(B43="","",MAX(0,B43-$B$6))</f>
-        <v>816922685</v>
+        <v>812022685</v>
       </c>
     </row>
     <row r="44" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -1977,7 +1977,7 @@
       </c>
       <c r="I44" s="15" t="n">
         <f aca="false">IF(B44="","",MAX(0,B44-$B$6))</f>
-        <v>1016922685</v>
+        <v>1012022685</v>
       </c>
     </row>
     <row r="45" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -2005,7 +2005,7 @@
       </c>
       <c r="I45" s="15" t="n">
         <f aca="false">IF(B45="","",MAX(0,B45-$B$6))</f>
-        <v>1216922685</v>
+        <v>1212022685</v>
       </c>
     </row>
     <row r="46" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -2033,7 +2033,7 @@
       </c>
       <c r="I46" s="15" t="n">
         <f aca="false">IF(B46="","",MAX(0,B46-$B$6))</f>
-        <v>1416922685</v>
+        <v>1412022685</v>
       </c>
     </row>
     <row r="47" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -2061,7 +2061,7 @@
       </c>
       <c r="I47" s="15" t="n">
         <f aca="false">IF(B47="","",MAX(0,B47-$B$6))</f>
-        <v>1616922685</v>
+        <v>1612022685</v>
       </c>
     </row>
     <row r="48" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -2089,7 +2089,7 @@
       </c>
       <c r="I48" s="15" t="n">
         <f aca="false">IF(B48="","",MAX(0,B48-$B$6))</f>
-        <v>1816922685</v>
+        <v>1812022685</v>
       </c>
     </row>
     <row r="49" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -2117,7 +2117,7 @@
       </c>
       <c r="I49" s="15" t="n">
         <f aca="false">IF(B49="","",MAX(0,B49-$B$6))</f>
-        <v>2016922685</v>
+        <v>2012022685</v>
       </c>
     </row>
     <row r="50" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -2145,7 +2145,7 @@
       </c>
       <c r="I50" s="15" t="n">
         <f aca="false">IF(B50="","",MAX(0,B50-$B$6))</f>
-        <v>2216922685</v>
+        <v>2212022685</v>
       </c>
     </row>
     <row r="51" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -2173,7 +2173,7 @@
       </c>
       <c r="I51" s="15" t="n">
         <f aca="false">IF(B51="","",MAX(0,B51-$B$6))</f>
-        <v>2416922685</v>
+        <v>2412022685</v>
       </c>
     </row>
     <row r="52" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -2201,7 +2201,7 @@
       </c>
       <c r="I52" s="15" t="n">
         <f aca="false">IF(B52="","",MAX(0,B52-$B$6))</f>
-        <v>2616922685</v>
+        <v>2612022685</v>
       </c>
     </row>
     <row r="53" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -2229,7 +2229,7 @@
       </c>
       <c r="I53" s="15" t="n">
         <f aca="false">IF(B53="","",MAX(0,B53-$B$6))</f>
-        <v>2816922685</v>
+        <v>2812022685</v>
       </c>
     </row>
     <row r="54" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -2257,7 +2257,7 @@
       </c>
       <c r="I54" s="15" t="n">
         <f aca="false">IF(B54="","",MAX(0,B54-$B$6))</f>
-        <v>3016922685</v>
+        <v>3012022685</v>
       </c>
     </row>
     <row r="56" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -2388,18 +2388,18 @@
         <v>500000000</v>
       </c>
       <c r="E6" s="11" t="n">
-        <v>153775315</v>
+        <v>158675315</v>
       </c>
       <c r="F6" s="15" t="n">
         <f aca="false">IF(ISNUMBER(D6),MAX(0,D6-N(E6)),"")</f>
-        <v>346224685</v>
+        <v>341324685</v>
       </c>
       <c r="G6" s="11" t="n">
-        <v>12860000</v>
+        <v>7690000</v>
       </c>
       <c r="H6" s="15" t="n">
         <f aca="false">IF(ISNUMBER(D6),MIN(N(G6)*N(C6),N(F6)),N(G6)*N(C6))</f>
-        <v>12860000</v>
+        <v>7690000</v>
       </c>
       <c r="I6" s="16" t="s">
         <v>91</v>
@@ -3061,7 +3061,7 @@
       </c>
       <c r="B32" s="7" t="n">
         <f aca="false">SUM(E5:E30)</f>
-        <v>394081815</v>
+        <v>398981815</v>
       </c>
     </row>
     <row r="33" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -3079,7 +3079,7 @@
       </c>
       <c r="B34" s="7" t="n">
         <f aca="false">'Iso Fest'!B6</f>
-        <v>483077315</v>
+        <v>487977315</v>
       </c>
     </row>
     <row r="35" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -3088,7 +3088,7 @@
       </c>
       <c r="B35" s="7" t="n">
         <f aca="false">SUM(H5:H30)</f>
-        <v>17860000</v>
+        <v>12690000</v>
       </c>
     </row>
     <row r="36" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -3097,7 +3097,7 @@
       </c>
       <c r="B36" s="7" t="n">
         <f aca="false">B34+B35</f>
-        <v>500937315</v>
+        <v>500667315</v>
       </c>
     </row>
     <row r="37" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -3115,7 +3115,7 @@
       </c>
       <c r="B38" s="7" t="n">
         <f aca="false">MAX(0,INDEX('Iso Fest'!B13:B54,'Iso Fest'!B9)-B36)</f>
-        <v>99062685</v>
+        <v>99332685</v>
       </c>
     </row>
     <row r="40" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">

--- a/Iso_Fest_Tracker.xlsx
+++ b/Iso_Fest_Tracker.xlsx
@@ -960,7 +960,7 @@
         <v>9</v>
       </c>
       <c r="B6" s="6" t="n">
-        <v>487977315</v>
+        <v>488127315</v>
       </c>
       <c r="D6" s="4" t="s">
         <v>10</v>
@@ -1008,7 +1008,7 @@
       </c>
       <c r="B8" s="7" t="n">
         <f aca="false">IFERROR(INDEX(I13:I54,MATCH(TRUE(),INDEX(B13:B54&gt;B6,0),0)),0)</f>
-        <v>12022685</v>
+        <v>11872685</v>
       </c>
     </row>
     <row r="9" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -1032,7 +1032,7 @@
       </c>
       <c r="B10" s="7" t="n">
         <f aca="false">MAX(0,INDEX(B13:B54,B9)-B6)</f>
-        <v>112022685</v>
+        <v>111872685</v>
       </c>
       <c r="D10" s="3" t="s">
         <v>17</v>
@@ -1048,7 +1048,7 @@
       </c>
       <c r="B11" s="7" t="n">
         <f aca="true">IFERROR(B10/MAX(B5-NOW(),0.01),0)</f>
-        <v>26416154.204047</v>
+        <v>26513224.9216101</v>
       </c>
     </row>
     <row r="12" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -1717,7 +1717,7 @@
       </c>
       <c r="I35" s="15" t="n">
         <f aca="false">IF(B35="","",MAX(0,B35-$B$6))</f>
-        <v>12022685</v>
+        <v>11872685</v>
       </c>
     </row>
     <row r="36" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -1745,7 +1745,7 @@
       </c>
       <c r="I36" s="15" t="n">
         <f aca="false">IF(B36="","",MAX(0,B36-$B$6))</f>
-        <v>37022685</v>
+        <v>36872685</v>
       </c>
     </row>
     <row r="37" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -1775,7 +1775,7 @@
       </c>
       <c r="I37" s="15" t="n">
         <f aca="false">IF(B37="","",MAX(0,B37-$B$6))</f>
-        <v>62022685</v>
+        <v>61872685</v>
       </c>
     </row>
     <row r="38" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -1803,7 +1803,7 @@
       </c>
       <c r="I38" s="15" t="n">
         <f aca="false">IF(B38="","",MAX(0,B38-$B$6))</f>
-        <v>112022685</v>
+        <v>111872685</v>
       </c>
     </row>
     <row r="39" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -1833,7 +1833,7 @@
       </c>
       <c r="I39" s="15" t="n">
         <f aca="false">IF(B39="","",MAX(0,B39-$B$6))</f>
-        <v>162022685</v>
+        <v>161872685</v>
       </c>
     </row>
     <row r="40" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -1861,7 +1861,7 @@
       </c>
       <c r="I40" s="15" t="n">
         <f aca="false">IF(B40="","",MAX(0,B40-$B$6))</f>
-        <v>262022685</v>
+        <v>261872685</v>
       </c>
     </row>
     <row r="41" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -1891,7 +1891,7 @@
       </c>
       <c r="I41" s="15" t="n">
         <f aca="false">IF(B41="","",MAX(0,B41-$B$6))</f>
-        <v>412022685</v>
+        <v>411872685</v>
       </c>
     </row>
     <row r="42" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -1919,7 +1919,7 @@
       </c>
       <c r="I42" s="15" t="n">
         <f aca="false">IF(B42="","",MAX(0,B42-$B$6))</f>
-        <v>612022685</v>
+        <v>611872685</v>
       </c>
     </row>
     <row r="43" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -1949,7 +1949,7 @@
       </c>
       <c r="I43" s="15" t="n">
         <f aca="false">IF(B43="","",MAX(0,B43-$B$6))</f>
-        <v>812022685</v>
+        <v>811872685</v>
       </c>
     </row>
     <row r="44" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -1977,7 +1977,7 @@
       </c>
       <c r="I44" s="15" t="n">
         <f aca="false">IF(B44="","",MAX(0,B44-$B$6))</f>
-        <v>1012022685</v>
+        <v>1011872685</v>
       </c>
     </row>
     <row r="45" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -2005,7 +2005,7 @@
       </c>
       <c r="I45" s="15" t="n">
         <f aca="false">IF(B45="","",MAX(0,B45-$B$6))</f>
-        <v>1212022685</v>
+        <v>1211872685</v>
       </c>
     </row>
     <row r="46" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -2033,7 +2033,7 @@
       </c>
       <c r="I46" s="15" t="n">
         <f aca="false">IF(B46="","",MAX(0,B46-$B$6))</f>
-        <v>1412022685</v>
+        <v>1411872685</v>
       </c>
     </row>
     <row r="47" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -2061,7 +2061,7 @@
       </c>
       <c r="I47" s="15" t="n">
         <f aca="false">IF(B47="","",MAX(0,B47-$B$6))</f>
-        <v>1612022685</v>
+        <v>1611872685</v>
       </c>
     </row>
     <row r="48" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -2089,7 +2089,7 @@
       </c>
       <c r="I48" s="15" t="n">
         <f aca="false">IF(B48="","",MAX(0,B48-$B$6))</f>
-        <v>1812022685</v>
+        <v>1811872685</v>
       </c>
     </row>
     <row r="49" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -2117,7 +2117,7 @@
       </c>
       <c r="I49" s="15" t="n">
         <f aca="false">IF(B49="","",MAX(0,B49-$B$6))</f>
-        <v>2012022685</v>
+        <v>2011872685</v>
       </c>
     </row>
     <row r="50" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -2145,7 +2145,7 @@
       </c>
       <c r="I50" s="15" t="n">
         <f aca="false">IF(B50="","",MAX(0,B50-$B$6))</f>
-        <v>2212022685</v>
+        <v>2211872685</v>
       </c>
     </row>
     <row r="51" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -2173,7 +2173,7 @@
       </c>
       <c r="I51" s="15" t="n">
         <f aca="false">IF(B51="","",MAX(0,B51-$B$6))</f>
-        <v>2412022685</v>
+        <v>2411872685</v>
       </c>
     </row>
     <row r="52" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -2201,7 +2201,7 @@
       </c>
       <c r="I52" s="15" t="n">
         <f aca="false">IF(B52="","",MAX(0,B52-$B$6))</f>
-        <v>2612022685</v>
+        <v>2611872685</v>
       </c>
     </row>
     <row r="53" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -2229,7 +2229,7 @@
       </c>
       <c r="I53" s="15" t="n">
         <f aca="false">IF(B53="","",MAX(0,B53-$B$6))</f>
-        <v>2812022685</v>
+        <v>2811872685</v>
       </c>
     </row>
     <row r="54" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -2257,7 +2257,7 @@
       </c>
       <c r="I54" s="15" t="n">
         <f aca="false">IF(B54="","",MAX(0,B54-$B$6))</f>
-        <v>3012022685</v>
+        <v>3011872685</v>
       </c>
     </row>
     <row r="56" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -2388,18 +2388,18 @@
         <v>500000000</v>
       </c>
       <c r="E6" s="11" t="n">
-        <v>158675315</v>
+        <v>158825315</v>
       </c>
       <c r="F6" s="15" t="n">
         <f aca="false">IF(ISNUMBER(D6),MAX(0,D6-N(E6)),"")</f>
-        <v>341324685</v>
+        <v>341174685</v>
       </c>
       <c r="G6" s="11" t="n">
-        <v>7690000</v>
+        <v>7540000</v>
       </c>
       <c r="H6" s="15" t="n">
         <f aca="false">IF(ISNUMBER(D6),MIN(N(G6)*N(C6),N(F6)),N(G6)*N(C6))</f>
-        <v>7690000</v>
+        <v>7540000</v>
       </c>
       <c r="I6" s="16" t="s">
         <v>91</v>
@@ -3061,7 +3061,7 @@
       </c>
       <c r="B32" s="7" t="n">
         <f aca="false">SUM(E5:E30)</f>
-        <v>398981815</v>
+        <v>399131815</v>
       </c>
     </row>
     <row r="33" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -3079,7 +3079,7 @@
       </c>
       <c r="B34" s="7" t="n">
         <f aca="false">'Iso Fest'!B6</f>
-        <v>487977315</v>
+        <v>488127315</v>
       </c>
     </row>
     <row r="35" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -3088,7 +3088,7 @@
       </c>
       <c r="B35" s="7" t="n">
         <f aca="false">SUM(H5:H30)</f>
-        <v>12690000</v>
+        <v>12540000</v>
       </c>
     </row>
     <row r="36" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">

--- a/Iso_Fest_Tracker.xlsx
+++ b/Iso_Fest_Tracker.xlsx
@@ -960,7 +960,7 @@
         <v>9</v>
       </c>
       <c r="B6" s="6" t="n">
-        <v>488127315</v>
+        <v>489819315</v>
       </c>
       <c r="D6" s="4" t="s">
         <v>10</v>
@@ -1008,7 +1008,7 @@
       </c>
       <c r="B8" s="7" t="n">
         <f aca="false">IFERROR(INDEX(I13:I54,MATCH(TRUE(),INDEX(B13:B54&gt;B6,0),0)),0)</f>
-        <v>11872685</v>
+        <v>10180685</v>
       </c>
     </row>
     <row r="9" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -1023,7 +1023,7 @@
       </c>
       <c r="G9" s="7" t="n">
         <f aca="false">Scoring!B36</f>
-        <v>500667315</v>
+        <v>502563315</v>
       </c>
     </row>
     <row r="10" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -1032,7 +1032,7 @@
       </c>
       <c r="B10" s="7" t="n">
         <f aca="false">MAX(0,INDEX(B13:B54,B9)-B6)</f>
-        <v>111872685</v>
+        <v>110180685</v>
       </c>
       <c r="D10" s="3" t="s">
         <v>17</v>
@@ -1048,7 +1048,7 @@
       </c>
       <c r="B11" s="7" t="n">
         <f aca="true">IFERROR(B10/MAX(B5-NOW(),0.01),0)</f>
-        <v>26513224.9216101</v>
+        <v>26146481.4953541</v>
       </c>
     </row>
     <row r="12" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -1717,7 +1717,7 @@
       </c>
       <c r="I35" s="15" t="n">
         <f aca="false">IF(B35="","",MAX(0,B35-$B$6))</f>
-        <v>11872685</v>
+        <v>10180685</v>
       </c>
     </row>
     <row r="36" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -1745,7 +1745,7 @@
       </c>
       <c r="I36" s="15" t="n">
         <f aca="false">IF(B36="","",MAX(0,B36-$B$6))</f>
-        <v>36872685</v>
+        <v>35180685</v>
       </c>
     </row>
     <row r="37" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -1775,7 +1775,7 @@
       </c>
       <c r="I37" s="15" t="n">
         <f aca="false">IF(B37="","",MAX(0,B37-$B$6))</f>
-        <v>61872685</v>
+        <v>60180685</v>
       </c>
     </row>
     <row r="38" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -1803,7 +1803,7 @@
       </c>
       <c r="I38" s="15" t="n">
         <f aca="false">IF(B38="","",MAX(0,B38-$B$6))</f>
-        <v>111872685</v>
+        <v>110180685</v>
       </c>
     </row>
     <row r="39" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -1833,7 +1833,7 @@
       </c>
       <c r="I39" s="15" t="n">
         <f aca="false">IF(B39="","",MAX(0,B39-$B$6))</f>
-        <v>161872685</v>
+        <v>160180685</v>
       </c>
     </row>
     <row r="40" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -1861,7 +1861,7 @@
       </c>
       <c r="I40" s="15" t="n">
         <f aca="false">IF(B40="","",MAX(0,B40-$B$6))</f>
-        <v>261872685</v>
+        <v>260180685</v>
       </c>
     </row>
     <row r="41" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -1891,7 +1891,7 @@
       </c>
       <c r="I41" s="15" t="n">
         <f aca="false">IF(B41="","",MAX(0,B41-$B$6))</f>
-        <v>411872685</v>
+        <v>410180685</v>
       </c>
     </row>
     <row r="42" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -1919,7 +1919,7 @@
       </c>
       <c r="I42" s="15" t="n">
         <f aca="false">IF(B42="","",MAX(0,B42-$B$6))</f>
-        <v>611872685</v>
+        <v>610180685</v>
       </c>
     </row>
     <row r="43" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -1949,7 +1949,7 @@
       </c>
       <c r="I43" s="15" t="n">
         <f aca="false">IF(B43="","",MAX(0,B43-$B$6))</f>
-        <v>811872685</v>
+        <v>810180685</v>
       </c>
     </row>
     <row r="44" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -1977,7 +1977,7 @@
       </c>
       <c r="I44" s="15" t="n">
         <f aca="false">IF(B44="","",MAX(0,B44-$B$6))</f>
-        <v>1011872685</v>
+        <v>1010180685</v>
       </c>
     </row>
     <row r="45" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -2005,7 +2005,7 @@
       </c>
       <c r="I45" s="15" t="n">
         <f aca="false">IF(B45="","",MAX(0,B45-$B$6))</f>
-        <v>1211872685</v>
+        <v>1210180685</v>
       </c>
     </row>
     <row r="46" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -2033,7 +2033,7 @@
       </c>
       <c r="I46" s="15" t="n">
         <f aca="false">IF(B46="","",MAX(0,B46-$B$6))</f>
-        <v>1411872685</v>
+        <v>1410180685</v>
       </c>
     </row>
     <row r="47" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -2061,7 +2061,7 @@
       </c>
       <c r="I47" s="15" t="n">
         <f aca="false">IF(B47="","",MAX(0,B47-$B$6))</f>
-        <v>1611872685</v>
+        <v>1610180685</v>
       </c>
     </row>
     <row r="48" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -2089,7 +2089,7 @@
       </c>
       <c r="I48" s="15" t="n">
         <f aca="false">IF(B48="","",MAX(0,B48-$B$6))</f>
-        <v>1811872685</v>
+        <v>1810180685</v>
       </c>
     </row>
     <row r="49" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -2117,7 +2117,7 @@
       </c>
       <c r="I49" s="15" t="n">
         <f aca="false">IF(B49="","",MAX(0,B49-$B$6))</f>
-        <v>2011872685</v>
+        <v>2010180685</v>
       </c>
     </row>
     <row r="50" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -2145,7 +2145,7 @@
       </c>
       <c r="I50" s="15" t="n">
         <f aca="false">IF(B50="","",MAX(0,B50-$B$6))</f>
-        <v>2211872685</v>
+        <v>2210180685</v>
       </c>
     </row>
     <row r="51" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -2173,7 +2173,7 @@
       </c>
       <c r="I51" s="15" t="n">
         <f aca="false">IF(B51="","",MAX(0,B51-$B$6))</f>
-        <v>2411872685</v>
+        <v>2410180685</v>
       </c>
     </row>
     <row r="52" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -2201,7 +2201,7 @@
       </c>
       <c r="I52" s="15" t="n">
         <f aca="false">IF(B52="","",MAX(0,B52-$B$6))</f>
-        <v>2611872685</v>
+        <v>2610180685</v>
       </c>
     </row>
     <row r="53" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -2229,7 +2229,7 @@
       </c>
       <c r="I53" s="15" t="n">
         <f aca="false">IF(B53="","",MAX(0,B53-$B$6))</f>
-        <v>2811872685</v>
+        <v>2810180685</v>
       </c>
     </row>
     <row r="54" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -2257,7 +2257,7 @@
       </c>
       <c r="I54" s="15" t="n">
         <f aca="false">IF(B54="","",MAX(0,B54-$B$6))</f>
-        <v>3011872685</v>
+        <v>3010180685</v>
       </c>
     </row>
     <row r="56" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -2388,18 +2388,18 @@
         <v>500000000</v>
       </c>
       <c r="E6" s="11" t="n">
-        <v>158825315</v>
+        <v>158675315</v>
       </c>
       <c r="F6" s="15" t="n">
         <f aca="false">IF(ISNUMBER(D6),MAX(0,D6-N(E6)),"")</f>
-        <v>341174685</v>
+        <v>341324685</v>
       </c>
       <c r="G6" s="11" t="n">
-        <v>7540000</v>
+        <v>7744000</v>
       </c>
       <c r="H6" s="15" t="n">
         <f aca="false">IF(ISNUMBER(D6),MIN(N(G6)*N(C6),N(F6)),N(G6)*N(C6))</f>
-        <v>7540000</v>
+        <v>7744000</v>
       </c>
       <c r="I6" s="16" t="s">
         <v>91</v>
@@ -2448,11 +2448,11 @@
         <v>500000000</v>
       </c>
       <c r="E8" s="11" t="n">
-        <v>58180000</v>
+        <v>58675000</v>
       </c>
       <c r="F8" s="15" t="n">
         <f aca="false">IF(ISNUMBER(D8),MAX(0,D8-N(E8)),"")</f>
-        <v>441820000</v>
+        <v>441325000</v>
       </c>
       <c r="G8" s="11"/>
       <c r="H8" s="15" t="n">
@@ -3061,7 +3061,7 @@
       </c>
       <c r="B32" s="7" t="n">
         <f aca="false">SUM(E5:E30)</f>
-        <v>399131815</v>
+        <v>399476815</v>
       </c>
     </row>
     <row r="33" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -3070,7 +3070,7 @@
       </c>
       <c r="B33" s="7" t="n">
         <f aca="false">'Iso Fest'!B6-B32</f>
-        <v>88995500</v>
+        <v>90342500</v>
       </c>
     </row>
     <row r="34" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -3079,7 +3079,7 @@
       </c>
       <c r="B34" s="7" t="n">
         <f aca="false">'Iso Fest'!B6</f>
-        <v>488127315</v>
+        <v>489819315</v>
       </c>
     </row>
     <row r="35" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -3088,7 +3088,7 @@
       </c>
       <c r="B35" s="7" t="n">
         <f aca="false">SUM(H5:H30)</f>
-        <v>12540000</v>
+        <v>12744000</v>
       </c>
     </row>
     <row r="36" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -3097,7 +3097,7 @@
       </c>
       <c r="B36" s="7" t="n">
         <f aca="false">B34+B35</f>
-        <v>500667315</v>
+        <v>502563315</v>
       </c>
     </row>
     <row r="37" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -3115,7 +3115,7 @@
       </c>
       <c r="B38" s="7" t="n">
         <f aca="false">MAX(0,INDEX('Iso Fest'!B13:B54,'Iso Fest'!B9)-B36)</f>
-        <v>99332685</v>
+        <v>97436685</v>
       </c>
     </row>
     <row r="40" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">

--- a/Iso_Fest_Tracker.xlsx
+++ b/Iso_Fest_Tracker.xlsx
@@ -960,7 +960,7 @@
         <v>9</v>
       </c>
       <c r="B6" s="6" t="n">
-        <v>489819315</v>
+        <v>490019315</v>
       </c>
       <c r="D6" s="4" t="s">
         <v>10</v>
@@ -1008,7 +1008,7 @@
       </c>
       <c r="B8" s="7" t="n">
         <f aca="false">IFERROR(INDEX(I13:I54,MATCH(TRUE(),INDEX(B13:B54&gt;B6,0),0)),0)</f>
-        <v>10180685</v>
+        <v>9980685</v>
       </c>
     </row>
     <row r="9" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -1023,7 +1023,7 @@
       </c>
       <c r="G9" s="7" t="n">
         <f aca="false">Scoring!B36</f>
-        <v>502563315</v>
+        <v>502413315</v>
       </c>
     </row>
     <row r="10" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -1032,7 +1032,7 @@
       </c>
       <c r="B10" s="7" t="n">
         <f aca="false">MAX(0,INDEX(B13:B54,B9)-B6)</f>
-        <v>110180685</v>
+        <v>109980685</v>
       </c>
       <c r="D10" s="3" t="s">
         <v>17</v>
@@ -1048,7 +1048,7 @@
       </c>
       <c r="B11" s="7" t="n">
         <f aca="true">IFERROR(B10/MAX(B5-NOW(),0.01),0)</f>
-        <v>26146481.4953541</v>
+        <v>26186696.534093</v>
       </c>
     </row>
     <row r="12" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -1717,7 +1717,7 @@
       </c>
       <c r="I35" s="15" t="n">
         <f aca="false">IF(B35="","",MAX(0,B35-$B$6))</f>
-        <v>10180685</v>
+        <v>9980685</v>
       </c>
     </row>
     <row r="36" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -1745,7 +1745,7 @@
       </c>
       <c r="I36" s="15" t="n">
         <f aca="false">IF(B36="","",MAX(0,B36-$B$6))</f>
-        <v>35180685</v>
+        <v>34980685</v>
       </c>
     </row>
     <row r="37" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -1775,7 +1775,7 @@
       </c>
       <c r="I37" s="15" t="n">
         <f aca="false">IF(B37="","",MAX(0,B37-$B$6))</f>
-        <v>60180685</v>
+        <v>59980685</v>
       </c>
     </row>
     <row r="38" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -1803,7 +1803,7 @@
       </c>
       <c r="I38" s="15" t="n">
         <f aca="false">IF(B38="","",MAX(0,B38-$B$6))</f>
-        <v>110180685</v>
+        <v>109980685</v>
       </c>
     </row>
     <row r="39" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -1833,7 +1833,7 @@
       </c>
       <c r="I39" s="15" t="n">
         <f aca="false">IF(B39="","",MAX(0,B39-$B$6))</f>
-        <v>160180685</v>
+        <v>159980685</v>
       </c>
     </row>
     <row r="40" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -1861,7 +1861,7 @@
       </c>
       <c r="I40" s="15" t="n">
         <f aca="false">IF(B40="","",MAX(0,B40-$B$6))</f>
-        <v>260180685</v>
+        <v>259980685</v>
       </c>
     </row>
     <row r="41" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -1891,7 +1891,7 @@
       </c>
       <c r="I41" s="15" t="n">
         <f aca="false">IF(B41="","",MAX(0,B41-$B$6))</f>
-        <v>410180685</v>
+        <v>409980685</v>
       </c>
     </row>
     <row r="42" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -1919,7 +1919,7 @@
       </c>
       <c r="I42" s="15" t="n">
         <f aca="false">IF(B42="","",MAX(0,B42-$B$6))</f>
-        <v>610180685</v>
+        <v>609980685</v>
       </c>
     </row>
     <row r="43" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -1949,7 +1949,7 @@
       </c>
       <c r="I43" s="15" t="n">
         <f aca="false">IF(B43="","",MAX(0,B43-$B$6))</f>
-        <v>810180685</v>
+        <v>809980685</v>
       </c>
     </row>
     <row r="44" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -1977,7 +1977,7 @@
       </c>
       <c r="I44" s="15" t="n">
         <f aca="false">IF(B44="","",MAX(0,B44-$B$6))</f>
-        <v>1010180685</v>
+        <v>1009980685</v>
       </c>
     </row>
     <row r="45" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -2005,7 +2005,7 @@
       </c>
       <c r="I45" s="15" t="n">
         <f aca="false">IF(B45="","",MAX(0,B45-$B$6))</f>
-        <v>1210180685</v>
+        <v>1209980685</v>
       </c>
     </row>
     <row r="46" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -2033,7 +2033,7 @@
       </c>
       <c r="I46" s="15" t="n">
         <f aca="false">IF(B46="","",MAX(0,B46-$B$6))</f>
-        <v>1410180685</v>
+        <v>1409980685</v>
       </c>
     </row>
     <row r="47" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -2061,7 +2061,7 @@
       </c>
       <c r="I47" s="15" t="n">
         <f aca="false">IF(B47="","",MAX(0,B47-$B$6))</f>
-        <v>1610180685</v>
+        <v>1609980685</v>
       </c>
     </row>
     <row r="48" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -2089,7 +2089,7 @@
       </c>
       <c r="I48" s="15" t="n">
         <f aca="false">IF(B48="","",MAX(0,B48-$B$6))</f>
-        <v>1810180685</v>
+        <v>1809980685</v>
       </c>
     </row>
     <row r="49" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -2117,7 +2117,7 @@
       </c>
       <c r="I49" s="15" t="n">
         <f aca="false">IF(B49="","",MAX(0,B49-$B$6))</f>
-        <v>2010180685</v>
+        <v>2009980685</v>
       </c>
     </row>
     <row r="50" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -2145,7 +2145,7 @@
       </c>
       <c r="I50" s="15" t="n">
         <f aca="false">IF(B50="","",MAX(0,B50-$B$6))</f>
-        <v>2210180685</v>
+        <v>2209980685</v>
       </c>
     </row>
     <row r="51" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -2173,7 +2173,7 @@
       </c>
       <c r="I51" s="15" t="n">
         <f aca="false">IF(B51="","",MAX(0,B51-$B$6))</f>
-        <v>2410180685</v>
+        <v>2409980685</v>
       </c>
     </row>
     <row r="52" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -2201,7 +2201,7 @@
       </c>
       <c r="I52" s="15" t="n">
         <f aca="false">IF(B52="","",MAX(0,B52-$B$6))</f>
-        <v>2610180685</v>
+        <v>2609980685</v>
       </c>
     </row>
     <row r="53" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -2229,7 +2229,7 @@
       </c>
       <c r="I53" s="15" t="n">
         <f aca="false">IF(B53="","",MAX(0,B53-$B$6))</f>
-        <v>2810180685</v>
+        <v>2809980685</v>
       </c>
     </row>
     <row r="54" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -2257,7 +2257,7 @@
       </c>
       <c r="I54" s="15" t="n">
         <f aca="false">IF(B54="","",MAX(0,B54-$B$6))</f>
-        <v>3010180685</v>
+        <v>3009980685</v>
       </c>
     </row>
     <row r="56" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -2388,18 +2388,18 @@
         <v>500000000</v>
       </c>
       <c r="E6" s="11" t="n">
-        <v>158675315</v>
+        <v>159025315</v>
       </c>
       <c r="F6" s="15" t="n">
         <f aca="false">IF(ISNUMBER(D6),MAX(0,D6-N(E6)),"")</f>
-        <v>341324685</v>
+        <v>340974685</v>
       </c>
       <c r="G6" s="11" t="n">
-        <v>7744000</v>
+        <v>7394000</v>
       </c>
       <c r="H6" s="15" t="n">
         <f aca="false">IF(ISNUMBER(D6),MIN(N(G6)*N(C6),N(F6)),N(G6)*N(C6))</f>
-        <v>7744000</v>
+        <v>7394000</v>
       </c>
       <c r="I6" s="16" t="s">
         <v>91</v>
@@ -3061,7 +3061,7 @@
       </c>
       <c r="B32" s="7" t="n">
         <f aca="false">SUM(E5:E30)</f>
-        <v>399476815</v>
+        <v>399826815</v>
       </c>
     </row>
     <row r="33" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -3070,7 +3070,7 @@
       </c>
       <c r="B33" s="7" t="n">
         <f aca="false">'Iso Fest'!B6-B32</f>
-        <v>90342500</v>
+        <v>90192500</v>
       </c>
     </row>
     <row r="34" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -3079,7 +3079,7 @@
       </c>
       <c r="B34" s="7" t="n">
         <f aca="false">'Iso Fest'!B6</f>
-        <v>489819315</v>
+        <v>490019315</v>
       </c>
     </row>
     <row r="35" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -3088,7 +3088,7 @@
       </c>
       <c r="B35" s="7" t="n">
         <f aca="false">SUM(H5:H30)</f>
-        <v>12744000</v>
+        <v>12394000</v>
       </c>
     </row>
     <row r="36" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -3097,7 +3097,7 @@
       </c>
       <c r="B36" s="7" t="n">
         <f aca="false">B34+B35</f>
-        <v>502563315</v>
+        <v>502413315</v>
       </c>
     </row>
     <row r="37" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -3115,7 +3115,7 @@
       </c>
       <c r="B38" s="7" t="n">
         <f aca="false">MAX(0,INDEX('Iso Fest'!B13:B54,'Iso Fest'!B9)-B36)</f>
-        <v>97436685</v>
+        <v>97586685</v>
       </c>
     </row>
     <row r="40" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">

--- a/Iso_Fest_Tracker.xlsx
+++ b/Iso_Fest_Tracker.xlsx
@@ -1023,7 +1023,7 @@
       </c>
       <c r="G9" s="7" t="n">
         <f aca="false">Scoring!B36</f>
-        <v>502413315</v>
+        <v>502849315</v>
       </c>
     </row>
     <row r="10" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -1048,7 +1048,7 @@
       </c>
       <c r="B11" s="7" t="n">
         <f aca="true">IFERROR(B10/MAX(B5-NOW(),0.01),0)</f>
-        <v>26186696.534093</v>
+        <v>28202280.8354329</v>
       </c>
     </row>
     <row r="12" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -2395,11 +2395,11 @@
         <v>340974685</v>
       </c>
       <c r="G6" s="11" t="n">
-        <v>7394000</v>
+        <v>7830000</v>
       </c>
       <c r="H6" s="15" t="n">
         <f aca="false">IF(ISNUMBER(D6),MIN(N(G6)*N(C6),N(F6)),N(G6)*N(C6))</f>
-        <v>7394000</v>
+        <v>7830000</v>
       </c>
       <c r="I6" s="16" t="s">
         <v>91</v>
@@ -3088,7 +3088,7 @@
       </c>
       <c r="B35" s="7" t="n">
         <f aca="false">SUM(H5:H30)</f>
-        <v>12394000</v>
+        <v>12830000</v>
       </c>
     </row>
     <row r="36" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -3097,7 +3097,7 @@
       </c>
       <c r="B36" s="7" t="n">
         <f aca="false">B34+B35</f>
-        <v>502413315</v>
+        <v>502849315</v>
       </c>
     </row>
     <row r="37" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -3115,7 +3115,7 @@
       </c>
       <c r="B38" s="7" t="n">
         <f aca="false">MAX(0,INDEX('Iso Fest'!B13:B54,'Iso Fest'!B9)-B36)</f>
-        <v>97586685</v>
+        <v>97150685</v>
       </c>
     </row>
     <row r="40" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">

--- a/Iso_Fest_Tracker.xlsx
+++ b/Iso_Fest_Tracker.xlsx
@@ -1023,7 +1023,7 @@
       </c>
       <c r="G9" s="7" t="n">
         <f aca="false">Scoring!B36</f>
-        <v>502849315</v>
+        <v>505824315</v>
       </c>
     </row>
     <row r="10" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -1048,7 +1048,7 @@
       </c>
       <c r="B11" s="7" t="n">
         <f aca="true">IFERROR(B10/MAX(B5-NOW(),0.01),0)</f>
-        <v>28202280.8354329</v>
+        <v>28209627.8745755</v>
       </c>
     </row>
     <row r="12" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -2395,11 +2395,11 @@
         <v>340974685</v>
       </c>
       <c r="G6" s="11" t="n">
-        <v>7830000</v>
+        <v>9650000</v>
       </c>
       <c r="H6" s="15" t="n">
         <f aca="false">IF(ISNUMBER(D6),MIN(N(G6)*N(C6),N(F6)),N(G6)*N(C6))</f>
-        <v>7830000</v>
+        <v>9650000</v>
       </c>
       <c r="I6" s="16" t="s">
         <v>91</v>
@@ -2454,10 +2454,12 @@
         <f aca="false">IF(ISNUMBER(D8),MAX(0,D8-N(E8)),"")</f>
         <v>441325000</v>
       </c>
-      <c r="G8" s="11"/>
+      <c r="G8" s="11" t="n">
+        <v>231</v>
+      </c>
       <c r="H8" s="15" t="n">
         <f aca="false">IF(ISNUMBER(D8),MIN(N(G8)*N(C8),N(F8)),N(G8)*N(C8))</f>
-        <v>0</v>
+        <v>1155000</v>
       </c>
       <c r="I8" s="16"/>
     </row>
@@ -3088,7 +3090,7 @@
       </c>
       <c r="B35" s="7" t="n">
         <f aca="false">SUM(H5:H30)</f>
-        <v>12830000</v>
+        <v>15805000</v>
       </c>
     </row>
     <row r="36" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -3097,7 +3099,7 @@
       </c>
       <c r="B36" s="7" t="n">
         <f aca="false">B34+B35</f>
-        <v>502849315</v>
+        <v>505824315</v>
       </c>
     </row>
     <row r="37" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -3115,7 +3117,7 @@
       </c>
       <c r="B38" s="7" t="n">
         <f aca="false">MAX(0,INDEX('Iso Fest'!B13:B54,'Iso Fest'!B9)-B36)</f>
-        <v>97150685</v>
+        <v>94175685</v>
       </c>
     </row>
     <row r="40" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">

--- a/Iso_Fest_Tracker.xlsx
+++ b/Iso_Fest_Tracker.xlsx
@@ -960,7 +960,7 @@
         <v>9</v>
       </c>
       <c r="B6" s="6" t="n">
-        <v>490019315</v>
+        <v>490119315</v>
       </c>
       <c r="D6" s="4" t="s">
         <v>10</v>
@@ -1008,7 +1008,7 @@
       </c>
       <c r="B8" s="7" t="n">
         <f aca="false">IFERROR(INDEX(I13:I54,MATCH(TRUE(),INDEX(B13:B54&gt;B6,0),0)),0)</f>
-        <v>9980685</v>
+        <v>9880685</v>
       </c>
     </row>
     <row r="9" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -1023,7 +1023,7 @@
       </c>
       <c r="G9" s="7" t="n">
         <f aca="false">Scoring!B36</f>
-        <v>505824315</v>
+        <v>505924315</v>
       </c>
     </row>
     <row r="10" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -1032,7 +1032,7 @@
       </c>
       <c r="B10" s="7" t="n">
         <f aca="false">MAX(0,INDEX(B13:B54,B9)-B6)</f>
-        <v>109980685</v>
+        <v>109880685</v>
       </c>
       <c r="D10" s="3" t="s">
         <v>17</v>
@@ -1048,7 +1048,7 @@
       </c>
       <c r="B11" s="7" t="n">
         <f aca="true">IFERROR(B10/MAX(B5-NOW(),0.01),0)</f>
-        <v>28209627.8745755</v>
+        <v>28225765.7306032</v>
       </c>
     </row>
     <row r="12" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -1717,7 +1717,7 @@
       </c>
       <c r="I35" s="15" t="n">
         <f aca="false">IF(B35="","",MAX(0,B35-$B$6))</f>
-        <v>9980685</v>
+        <v>9880685</v>
       </c>
     </row>
     <row r="36" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -1745,7 +1745,7 @@
       </c>
       <c r="I36" s="15" t="n">
         <f aca="false">IF(B36="","",MAX(0,B36-$B$6))</f>
-        <v>34980685</v>
+        <v>34880685</v>
       </c>
     </row>
     <row r="37" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -1775,7 +1775,7 @@
       </c>
       <c r="I37" s="15" t="n">
         <f aca="false">IF(B37="","",MAX(0,B37-$B$6))</f>
-        <v>59980685</v>
+        <v>59880685</v>
       </c>
     </row>
     <row r="38" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -1803,7 +1803,7 @@
       </c>
       <c r="I38" s="15" t="n">
         <f aca="false">IF(B38="","",MAX(0,B38-$B$6))</f>
-        <v>109980685</v>
+        <v>109880685</v>
       </c>
     </row>
     <row r="39" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -1833,7 +1833,7 @@
       </c>
       <c r="I39" s="15" t="n">
         <f aca="false">IF(B39="","",MAX(0,B39-$B$6))</f>
-        <v>159980685</v>
+        <v>159880685</v>
       </c>
     </row>
     <row r="40" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -1861,7 +1861,7 @@
       </c>
       <c r="I40" s="15" t="n">
         <f aca="false">IF(B40="","",MAX(0,B40-$B$6))</f>
-        <v>259980685</v>
+        <v>259880685</v>
       </c>
     </row>
     <row r="41" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -1891,7 +1891,7 @@
       </c>
       <c r="I41" s="15" t="n">
         <f aca="false">IF(B41="","",MAX(0,B41-$B$6))</f>
-        <v>409980685</v>
+        <v>409880685</v>
       </c>
     </row>
     <row r="42" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -1919,7 +1919,7 @@
       </c>
       <c r="I42" s="15" t="n">
         <f aca="false">IF(B42="","",MAX(0,B42-$B$6))</f>
-        <v>609980685</v>
+        <v>609880685</v>
       </c>
     </row>
     <row r="43" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -1949,7 +1949,7 @@
       </c>
       <c r="I43" s="15" t="n">
         <f aca="false">IF(B43="","",MAX(0,B43-$B$6))</f>
-        <v>809980685</v>
+        <v>809880685</v>
       </c>
     </row>
     <row r="44" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -1977,7 +1977,7 @@
       </c>
       <c r="I44" s="15" t="n">
         <f aca="false">IF(B44="","",MAX(0,B44-$B$6))</f>
-        <v>1009980685</v>
+        <v>1009880685</v>
       </c>
     </row>
     <row r="45" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -2005,7 +2005,7 @@
       </c>
       <c r="I45" s="15" t="n">
         <f aca="false">IF(B45="","",MAX(0,B45-$B$6))</f>
-        <v>1209980685</v>
+        <v>1209880685</v>
       </c>
     </row>
     <row r="46" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -2033,7 +2033,7 @@
       </c>
       <c r="I46" s="15" t="n">
         <f aca="false">IF(B46="","",MAX(0,B46-$B$6))</f>
-        <v>1409980685</v>
+        <v>1409880685</v>
       </c>
     </row>
     <row r="47" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -2061,7 +2061,7 @@
       </c>
       <c r="I47" s="15" t="n">
         <f aca="false">IF(B47="","",MAX(0,B47-$B$6))</f>
-        <v>1609980685</v>
+        <v>1609880685</v>
       </c>
     </row>
     <row r="48" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -2089,7 +2089,7 @@
       </c>
       <c r="I48" s="15" t="n">
         <f aca="false">IF(B48="","",MAX(0,B48-$B$6))</f>
-        <v>1809980685</v>
+        <v>1809880685</v>
       </c>
     </row>
     <row r="49" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -2117,7 +2117,7 @@
       </c>
       <c r="I49" s="15" t="n">
         <f aca="false">IF(B49="","",MAX(0,B49-$B$6))</f>
-        <v>2009980685</v>
+        <v>2009880685</v>
       </c>
     </row>
     <row r="50" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -2145,7 +2145,7 @@
       </c>
       <c r="I50" s="15" t="n">
         <f aca="false">IF(B50="","",MAX(0,B50-$B$6))</f>
-        <v>2209980685</v>
+        <v>2209880685</v>
       </c>
     </row>
     <row r="51" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -2173,7 +2173,7 @@
       </c>
       <c r="I51" s="15" t="n">
         <f aca="false">IF(B51="","",MAX(0,B51-$B$6))</f>
-        <v>2409980685</v>
+        <v>2409880685</v>
       </c>
     </row>
     <row r="52" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -2201,7 +2201,7 @@
       </c>
       <c r="I52" s="15" t="n">
         <f aca="false">IF(B52="","",MAX(0,B52-$B$6))</f>
-        <v>2609980685</v>
+        <v>2609880685</v>
       </c>
     </row>
     <row r="53" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -2229,7 +2229,7 @@
       </c>
       <c r="I53" s="15" t="n">
         <f aca="false">IF(B53="","",MAX(0,B53-$B$6))</f>
-        <v>2809980685</v>
+        <v>2809880685</v>
       </c>
     </row>
     <row r="54" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -2257,7 +2257,7 @@
       </c>
       <c r="I54" s="15" t="n">
         <f aca="false">IF(B54="","",MAX(0,B54-$B$6))</f>
-        <v>3009980685</v>
+        <v>3009880685</v>
       </c>
     </row>
     <row r="56" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -2419,11 +2419,11 @@
         <v>250000000</v>
       </c>
       <c r="E7" s="11" t="n">
-        <v>10300000</v>
+        <v>10400000</v>
       </c>
       <c r="F7" s="15" t="n">
         <f aca="false">IF(ISNUMBER(D7),MAX(0,D7-N(E7)),"")</f>
-        <v>239700000</v>
+        <v>239600000</v>
       </c>
       <c r="G7" s="11"/>
       <c r="H7" s="15" t="n">
@@ -3063,7 +3063,7 @@
       </c>
       <c r="B32" s="7" t="n">
         <f aca="false">SUM(E5:E30)</f>
-        <v>399826815</v>
+        <v>399926815</v>
       </c>
     </row>
     <row r="33" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -3081,7 +3081,7 @@
       </c>
       <c r="B34" s="7" t="n">
         <f aca="false">'Iso Fest'!B6</f>
-        <v>490019315</v>
+        <v>490119315</v>
       </c>
     </row>
     <row r="35" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -3099,7 +3099,7 @@
       </c>
       <c r="B36" s="7" t="n">
         <f aca="false">B34+B35</f>
-        <v>505824315</v>
+        <v>505924315</v>
       </c>
     </row>
     <row r="37" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -3117,7 +3117,7 @@
       </c>
       <c r="B38" s="7" t="n">
         <f aca="false">MAX(0,INDEX('Iso Fest'!B13:B54,'Iso Fest'!B9)-B36)</f>
-        <v>94175685</v>
+        <v>94075685</v>
       </c>
     </row>
     <row r="40" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">

--- a/Iso_Fest_Tracker.xlsx
+++ b/Iso_Fest_Tracker.xlsx
@@ -362,7 +362,7 @@
     <t xml:space="preserve">Cosmic character to T3 L5</t>
   </si>
   <si>
-    <t xml:space="preserve">Mephisto planned after milestone 24</t>
+    <t xml:space="preserve">Mephisto done Oct 14</t>
   </si>
   <si>
     <t xml:space="preserve">Global character to T3 L5</t>
@@ -960,7 +960,7 @@
         <v>9</v>
       </c>
       <c r="B6" s="6" t="n">
-        <v>490119315</v>
+        <v>500471615</v>
       </c>
       <c r="D6" s="4" t="s">
         <v>10</v>
@@ -984,7 +984,7 @@
       </c>
       <c r="B7" s="3" t="n">
         <f aca="false">IFERROR(INDEX(A13:A54,MATCH(TRUE(),INDEX(B13:B54&gt;B6,0),0)),"All done")</f>
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="D7" s="4" t="s">
         <v>12</v>
@@ -995,11 +995,11 @@
       </c>
       <c r="F7" s="7" t="n">
         <f aca="false">SUMPRODUCT((B13:B54&lt;&gt;"")*(B13:B54&lt;=$B$6)*(H13:H54&lt;&gt;"Claimed")*F13:F54)</f>
-        <v>0</v>
+        <v>1400000</v>
       </c>
       <c r="G7" s="7" t="n">
         <f aca="false">SUMPRODUCT((B13:B54&lt;&gt;"")*(B13:B54&lt;=$B$6)*(H13:H54&lt;&gt;"Claimed")*G13:G54)</f>
-        <v>0</v>
+        <v>1900000</v>
       </c>
     </row>
     <row r="8" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -1008,7 +1008,7 @@
       </c>
       <c r="B8" s="7" t="n">
         <f aca="false">IFERROR(INDEX(I13:I54,MATCH(TRUE(),INDEX(B13:B54&gt;B6,0),0)),0)</f>
-        <v>9880685</v>
+        <v>24528385</v>
       </c>
     </row>
     <row r="9" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -1023,7 +1023,7 @@
       </c>
       <c r="G9" s="7" t="n">
         <f aca="false">Scoring!B36</f>
-        <v>505924315</v>
+        <v>511276615</v>
       </c>
     </row>
     <row r="10" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -1032,7 +1032,7 @@
       </c>
       <c r="B10" s="7" t="n">
         <f aca="false">MAX(0,INDEX(B13:B54,B9)-B6)</f>
-        <v>109880685</v>
+        <v>99528385</v>
       </c>
       <c r="D10" s="3" t="s">
         <v>17</v>
@@ -1048,7 +1048,7 @@
       </c>
       <c r="B11" s="7" t="n">
         <f aca="true">IFERROR(B10/MAX(B5-NOW(),0.01),0)</f>
-        <v>28225765.7306032</v>
+        <v>25856650.8335243</v>
       </c>
     </row>
     <row r="12" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -1717,7 +1717,7 @@
       </c>
       <c r="I35" s="15" t="n">
         <f aca="false">IF(B35="","",MAX(0,B35-$B$6))</f>
-        <v>9880685</v>
+        <v>0</v>
       </c>
     </row>
     <row r="36" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -1745,7 +1745,7 @@
       </c>
       <c r="I36" s="15" t="n">
         <f aca="false">IF(B36="","",MAX(0,B36-$B$6))</f>
-        <v>34880685</v>
+        <v>24528385</v>
       </c>
     </row>
     <row r="37" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -1775,7 +1775,7 @@
       </c>
       <c r="I37" s="15" t="n">
         <f aca="false">IF(B37="","",MAX(0,B37-$B$6))</f>
-        <v>59880685</v>
+        <v>49528385</v>
       </c>
     </row>
     <row r="38" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -1803,7 +1803,7 @@
       </c>
       <c r="I38" s="15" t="n">
         <f aca="false">IF(B38="","",MAX(0,B38-$B$6))</f>
-        <v>109880685</v>
+        <v>99528385</v>
       </c>
     </row>
     <row r="39" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -1833,7 +1833,7 @@
       </c>
       <c r="I39" s="15" t="n">
         <f aca="false">IF(B39="","",MAX(0,B39-$B$6))</f>
-        <v>159880685</v>
+        <v>149528385</v>
       </c>
     </row>
     <row r="40" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -1861,7 +1861,7 @@
       </c>
       <c r="I40" s="15" t="n">
         <f aca="false">IF(B40="","",MAX(0,B40-$B$6))</f>
-        <v>259880685</v>
+        <v>249528385</v>
       </c>
     </row>
     <row r="41" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -1891,7 +1891,7 @@
       </c>
       <c r="I41" s="15" t="n">
         <f aca="false">IF(B41="","",MAX(0,B41-$B$6))</f>
-        <v>409880685</v>
+        <v>399528385</v>
       </c>
     </row>
     <row r="42" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -1919,7 +1919,7 @@
       </c>
       <c r="I42" s="15" t="n">
         <f aca="false">IF(B42="","",MAX(0,B42-$B$6))</f>
-        <v>609880685</v>
+        <v>599528385</v>
       </c>
     </row>
     <row r="43" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -1949,7 +1949,7 @@
       </c>
       <c r="I43" s="15" t="n">
         <f aca="false">IF(B43="","",MAX(0,B43-$B$6))</f>
-        <v>809880685</v>
+        <v>799528385</v>
       </c>
     </row>
     <row r="44" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -1977,7 +1977,7 @@
       </c>
       <c r="I44" s="15" t="n">
         <f aca="false">IF(B44="","",MAX(0,B44-$B$6))</f>
-        <v>1009880685</v>
+        <v>999528385</v>
       </c>
     </row>
     <row r="45" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -2005,7 +2005,7 @@
       </c>
       <c r="I45" s="15" t="n">
         <f aca="false">IF(B45="","",MAX(0,B45-$B$6))</f>
-        <v>1209880685</v>
+        <v>1199528385</v>
       </c>
     </row>
     <row r="46" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -2033,7 +2033,7 @@
       </c>
       <c r="I46" s="15" t="n">
         <f aca="false">IF(B46="","",MAX(0,B46-$B$6))</f>
-        <v>1409880685</v>
+        <v>1399528385</v>
       </c>
     </row>
     <row r="47" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -2061,7 +2061,7 @@
       </c>
       <c r="I47" s="15" t="n">
         <f aca="false">IF(B47="","",MAX(0,B47-$B$6))</f>
-        <v>1609880685</v>
+        <v>1599528385</v>
       </c>
     </row>
     <row r="48" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -2089,7 +2089,7 @@
       </c>
       <c r="I48" s="15" t="n">
         <f aca="false">IF(B48="","",MAX(0,B48-$B$6))</f>
-        <v>1809880685</v>
+        <v>1799528385</v>
       </c>
     </row>
     <row r="49" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -2117,7 +2117,7 @@
       </c>
       <c r="I49" s="15" t="n">
         <f aca="false">IF(B49="","",MAX(0,B49-$B$6))</f>
-        <v>2009880685</v>
+        <v>1999528385</v>
       </c>
     </row>
     <row r="50" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -2145,7 +2145,7 @@
       </c>
       <c r="I50" s="15" t="n">
         <f aca="false">IF(B50="","",MAX(0,B50-$B$6))</f>
-        <v>2209880685</v>
+        <v>2199528385</v>
       </c>
     </row>
     <row r="51" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -2173,7 +2173,7 @@
       </c>
       <c r="I51" s="15" t="n">
         <f aca="false">IF(B51="","",MAX(0,B51-$B$6))</f>
-        <v>2409880685</v>
+        <v>2399528385</v>
       </c>
     </row>
     <row r="52" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -2201,7 +2201,7 @@
       </c>
       <c r="I52" s="15" t="n">
         <f aca="false">IF(B52="","",MAX(0,B52-$B$6))</f>
-        <v>2609880685</v>
+        <v>2599528385</v>
       </c>
     </row>
     <row r="53" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -2229,7 +2229,7 @@
       </c>
       <c r="I53" s="15" t="n">
         <f aca="false">IF(B53="","",MAX(0,B53-$B$6))</f>
-        <v>2809880685</v>
+        <v>2799528385</v>
       </c>
     </row>
     <row r="54" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -2257,7 +2257,7 @@
       </c>
       <c r="I54" s="15" t="n">
         <f aca="false">IF(B54="","",MAX(0,B54-$B$6))</f>
-        <v>3009880685</v>
+        <v>2999528385</v>
       </c>
     </row>
     <row r="56" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -2832,18 +2832,16 @@
         <v>25000000</v>
       </c>
       <c r="E22" s="11" t="n">
-        <v>20000000</v>
+        <v>25000000</v>
       </c>
       <c r="F22" s="15" t="n">
         <f aca="false">IF(ISNUMBER(D22),MAX(0,D22-N(E22)),"")</f>
-        <v>5000000</v>
-      </c>
-      <c r="G22" s="11" t="n">
-        <v>1</v>
-      </c>
+        <v>0</v>
+      </c>
+      <c r="G22" s="11"/>
       <c r="H22" s="15" t="n">
         <f aca="false">IF(ISNUMBER(D22),MIN(N(G22)*N(C22),N(F22)),N(G22)*N(C22))</f>
-        <v>5000000</v>
+        <v>0</v>
       </c>
       <c r="I22" s="16" t="s">
         <v>113</v>
@@ -3063,7 +3061,7 @@
       </c>
       <c r="B32" s="7" t="n">
         <f aca="false">SUM(E5:E30)</f>
-        <v>399926815</v>
+        <v>404926815</v>
       </c>
     </row>
     <row r="33" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -3072,7 +3070,7 @@
       </c>
       <c r="B33" s="7" t="n">
         <f aca="false">'Iso Fest'!B6-B32</f>
-        <v>90192500</v>
+        <v>95544800</v>
       </c>
     </row>
     <row r="34" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -3081,7 +3079,7 @@
       </c>
       <c r="B34" s="7" t="n">
         <f aca="false">'Iso Fest'!B6</f>
-        <v>490119315</v>
+        <v>500471615</v>
       </c>
     </row>
     <row r="35" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -3090,7 +3088,7 @@
       </c>
       <c r="B35" s="7" t="n">
         <f aca="false">SUM(H5:H30)</f>
-        <v>15805000</v>
+        <v>10805000</v>
       </c>
     </row>
     <row r="36" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -3099,7 +3097,7 @@
       </c>
       <c r="B36" s="7" t="n">
         <f aca="false">B34+B35</f>
-        <v>505924315</v>
+        <v>511276615</v>
       </c>
     </row>
     <row r="37" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -3117,7 +3115,7 @@
       </c>
       <c r="B38" s="7" t="n">
         <f aca="false">MAX(0,INDEX('Iso Fest'!B13:B54,'Iso Fest'!B9)-B36)</f>
-        <v>94075685</v>
+        <v>88723385</v>
       </c>
     </row>
     <row r="40" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">

--- a/Iso_Fest_Tracker.xlsx
+++ b/Iso_Fest_Tracker.xlsx
@@ -960,7 +960,7 @@
         <v>9</v>
       </c>
       <c r="B6" s="6" t="n">
-        <v>500471615</v>
+        <v>500571615</v>
       </c>
       <c r="D6" s="4" t="s">
         <v>10</v>
@@ -1008,7 +1008,7 @@
       </c>
       <c r="B8" s="7" t="n">
         <f aca="false">IFERROR(INDEX(I13:I54,MATCH(TRUE(),INDEX(B13:B54&gt;B6,0),0)),0)</f>
-        <v>24528385</v>
+        <v>24428385</v>
       </c>
     </row>
     <row r="9" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -1023,7 +1023,7 @@
       </c>
       <c r="G9" s="7" t="n">
         <f aca="false">Scoring!B36</f>
-        <v>511276615</v>
+        <v>511376615</v>
       </c>
     </row>
     <row r="10" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -1032,7 +1032,7 @@
       </c>
       <c r="B10" s="7" t="n">
         <f aca="false">MAX(0,INDEX(B13:B54,B9)-B6)</f>
-        <v>99528385</v>
+        <v>99428385</v>
       </c>
       <c r="D10" s="3" t="s">
         <v>17</v>
@@ -1048,7 +1048,7 @@
       </c>
       <c r="B11" s="7" t="n">
         <f aca="true">IFERROR(B10/MAX(B5-NOW(),0.01),0)</f>
-        <v>25856650.8335243</v>
+        <v>28688750.0299066</v>
       </c>
     </row>
     <row r="12" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -1745,7 +1745,7 @@
       </c>
       <c r="I36" s="15" t="n">
         <f aca="false">IF(B36="","",MAX(0,B36-$B$6))</f>
-        <v>24528385</v>
+        <v>24428385</v>
       </c>
     </row>
     <row r="37" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -1775,7 +1775,7 @@
       </c>
       <c r="I37" s="15" t="n">
         <f aca="false">IF(B37="","",MAX(0,B37-$B$6))</f>
-        <v>49528385</v>
+        <v>49428385</v>
       </c>
     </row>
     <row r="38" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -1803,7 +1803,7 @@
       </c>
       <c r="I38" s="15" t="n">
         <f aca="false">IF(B38="","",MAX(0,B38-$B$6))</f>
-        <v>99528385</v>
+        <v>99428385</v>
       </c>
     </row>
     <row r="39" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -1833,7 +1833,7 @@
       </c>
       <c r="I39" s="15" t="n">
         <f aca="false">IF(B39="","",MAX(0,B39-$B$6))</f>
-        <v>149528385</v>
+        <v>149428385</v>
       </c>
     </row>
     <row r="40" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -1861,7 +1861,7 @@
       </c>
       <c r="I40" s="15" t="n">
         <f aca="false">IF(B40="","",MAX(0,B40-$B$6))</f>
-        <v>249528385</v>
+        <v>249428385</v>
       </c>
     </row>
     <row r="41" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -1891,7 +1891,7 @@
       </c>
       <c r="I41" s="15" t="n">
         <f aca="false">IF(B41="","",MAX(0,B41-$B$6))</f>
-        <v>399528385</v>
+        <v>399428385</v>
       </c>
     </row>
     <row r="42" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -1919,7 +1919,7 @@
       </c>
       <c r="I42" s="15" t="n">
         <f aca="false">IF(B42="","",MAX(0,B42-$B$6))</f>
-        <v>599528385</v>
+        <v>599428385</v>
       </c>
     </row>
     <row r="43" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -1949,7 +1949,7 @@
       </c>
       <c r="I43" s="15" t="n">
         <f aca="false">IF(B43="","",MAX(0,B43-$B$6))</f>
-        <v>799528385</v>
+        <v>799428385</v>
       </c>
     </row>
     <row r="44" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -1977,7 +1977,7 @@
       </c>
       <c r="I44" s="15" t="n">
         <f aca="false">IF(B44="","",MAX(0,B44-$B$6))</f>
-        <v>999528385</v>
+        <v>999428385</v>
       </c>
     </row>
     <row r="45" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -2005,7 +2005,7 @@
       </c>
       <c r="I45" s="15" t="n">
         <f aca="false">IF(B45="","",MAX(0,B45-$B$6))</f>
-        <v>1199528385</v>
+        <v>1199428385</v>
       </c>
     </row>
     <row r="46" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -2033,7 +2033,7 @@
       </c>
       <c r="I46" s="15" t="n">
         <f aca="false">IF(B46="","",MAX(0,B46-$B$6))</f>
-        <v>1399528385</v>
+        <v>1399428385</v>
       </c>
     </row>
     <row r="47" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -2061,7 +2061,7 @@
       </c>
       <c r="I47" s="15" t="n">
         <f aca="false">IF(B47="","",MAX(0,B47-$B$6))</f>
-        <v>1599528385</v>
+        <v>1599428385</v>
       </c>
     </row>
     <row r="48" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -2089,7 +2089,7 @@
       </c>
       <c r="I48" s="15" t="n">
         <f aca="false">IF(B48="","",MAX(0,B48-$B$6))</f>
-        <v>1799528385</v>
+        <v>1799428385</v>
       </c>
     </row>
     <row r="49" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -2117,7 +2117,7 @@
       </c>
       <c r="I49" s="15" t="n">
         <f aca="false">IF(B49="","",MAX(0,B49-$B$6))</f>
-        <v>1999528385</v>
+        <v>1999428385</v>
       </c>
     </row>
     <row r="50" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -2145,7 +2145,7 @@
       </c>
       <c r="I50" s="15" t="n">
         <f aca="false">IF(B50="","",MAX(0,B50-$B$6))</f>
-        <v>2199528385</v>
+        <v>2199428385</v>
       </c>
     </row>
     <row r="51" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -2173,7 +2173,7 @@
       </c>
       <c r="I51" s="15" t="n">
         <f aca="false">IF(B51="","",MAX(0,B51-$B$6))</f>
-        <v>2399528385</v>
+        <v>2399428385</v>
       </c>
     </row>
     <row r="52" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -2201,7 +2201,7 @@
       </c>
       <c r="I52" s="15" t="n">
         <f aca="false">IF(B52="","",MAX(0,B52-$B$6))</f>
-        <v>2599528385</v>
+        <v>2599428385</v>
       </c>
     </row>
     <row r="53" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -2229,7 +2229,7 @@
       </c>
       <c r="I53" s="15" t="n">
         <f aca="false">IF(B53="","",MAX(0,B53-$B$6))</f>
-        <v>2799528385</v>
+        <v>2799428385</v>
       </c>
     </row>
     <row r="54" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -2257,7 +2257,7 @@
       </c>
       <c r="I54" s="15" t="n">
         <f aca="false">IF(B54="","",MAX(0,B54-$B$6))</f>
-        <v>2999528385</v>
+        <v>2999428385</v>
       </c>
     </row>
     <row r="56" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -2419,11 +2419,11 @@
         <v>250000000</v>
       </c>
       <c r="E7" s="11" t="n">
-        <v>10400000</v>
+        <v>10500000</v>
       </c>
       <c r="F7" s="15" t="n">
         <f aca="false">IF(ISNUMBER(D7),MAX(0,D7-N(E7)),"")</f>
-        <v>239600000</v>
+        <v>239500000</v>
       </c>
       <c r="G7" s="11"/>
       <c r="H7" s="15" t="n">
@@ -3061,7 +3061,7 @@
       </c>
       <c r="B32" s="7" t="n">
         <f aca="false">SUM(E5:E30)</f>
-        <v>404926815</v>
+        <v>405026815</v>
       </c>
     </row>
     <row r="33" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -3079,7 +3079,7 @@
       </c>
       <c r="B34" s="7" t="n">
         <f aca="false">'Iso Fest'!B6</f>
-        <v>500471615</v>
+        <v>500571615</v>
       </c>
     </row>
     <row r="35" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -3097,7 +3097,7 @@
       </c>
       <c r="B36" s="7" t="n">
         <f aca="false">B34+B35</f>
-        <v>511276615</v>
+        <v>511376615</v>
       </c>
     </row>
     <row r="37" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -3115,7 +3115,7 @@
       </c>
       <c r="B38" s="7" t="n">
         <f aca="false">MAX(0,INDEX('Iso Fest'!B13:B54,'Iso Fest'!B9)-B36)</f>
-        <v>88723385</v>
+        <v>88623385</v>
       </c>
     </row>
     <row r="40" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">

--- a/Iso_Fest_Tracker.xlsx
+++ b/Iso_Fest_Tracker.xlsx
@@ -960,7 +960,7 @@
         <v>9</v>
       </c>
       <c r="B6" s="6" t="n">
-        <v>500571615</v>
+        <v>504814310</v>
       </c>
       <c r="D6" s="4" t="s">
         <v>10</v>
@@ -1008,7 +1008,7 @@
       </c>
       <c r="B8" s="7" t="n">
         <f aca="false">IFERROR(INDEX(I13:I54,MATCH(TRUE(),INDEX(B13:B54&gt;B6,0),0)),0)</f>
-        <v>24428385</v>
+        <v>20185690</v>
       </c>
     </row>
     <row r="9" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -1023,7 +1023,7 @@
       </c>
       <c r="G9" s="7" t="n">
         <f aca="false">Scoring!B36</f>
-        <v>511376615</v>
+        <v>514209310</v>
       </c>
     </row>
     <row r="10" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -1032,7 +1032,7 @@
       </c>
       <c r="B10" s="7" t="n">
         <f aca="false">MAX(0,INDEX(B13:B54,B9)-B6)</f>
-        <v>99428385</v>
+        <v>95185690</v>
       </c>
       <c r="D10" s="3" t="s">
         <v>17</v>
@@ -1048,7 +1048,7 @@
       </c>
       <c r="B11" s="7" t="n">
         <f aca="true">IFERROR(B10/MAX(B5-NOW(),0.01),0)</f>
-        <v>28688750.0299066</v>
+        <v>29028374.8208475</v>
       </c>
     </row>
     <row r="12" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -1745,7 +1745,7 @@
       </c>
       <c r="I36" s="15" t="n">
         <f aca="false">IF(B36="","",MAX(0,B36-$B$6))</f>
-        <v>24428385</v>
+        <v>20185690</v>
       </c>
     </row>
     <row r="37" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -1775,7 +1775,7 @@
       </c>
       <c r="I37" s="15" t="n">
         <f aca="false">IF(B37="","",MAX(0,B37-$B$6))</f>
-        <v>49428385</v>
+        <v>45185690</v>
       </c>
     </row>
     <row r="38" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -1803,7 +1803,7 @@
       </c>
       <c r="I38" s="15" t="n">
         <f aca="false">IF(B38="","",MAX(0,B38-$B$6))</f>
-        <v>99428385</v>
+        <v>95185690</v>
       </c>
     </row>
     <row r="39" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -1833,7 +1833,7 @@
       </c>
       <c r="I39" s="15" t="n">
         <f aca="false">IF(B39="","",MAX(0,B39-$B$6))</f>
-        <v>149428385</v>
+        <v>145185690</v>
       </c>
     </row>
     <row r="40" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -1861,7 +1861,7 @@
       </c>
       <c r="I40" s="15" t="n">
         <f aca="false">IF(B40="","",MAX(0,B40-$B$6))</f>
-        <v>249428385</v>
+        <v>245185690</v>
       </c>
     </row>
     <row r="41" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -1891,7 +1891,7 @@
       </c>
       <c r="I41" s="15" t="n">
         <f aca="false">IF(B41="","",MAX(0,B41-$B$6))</f>
-        <v>399428385</v>
+        <v>395185690</v>
       </c>
     </row>
     <row r="42" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -1919,7 +1919,7 @@
       </c>
       <c r="I42" s="15" t="n">
         <f aca="false">IF(B42="","",MAX(0,B42-$B$6))</f>
-        <v>599428385</v>
+        <v>595185690</v>
       </c>
     </row>
     <row r="43" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -1949,7 +1949,7 @@
       </c>
       <c r="I43" s="15" t="n">
         <f aca="false">IF(B43="","",MAX(0,B43-$B$6))</f>
-        <v>799428385</v>
+        <v>795185690</v>
       </c>
     </row>
     <row r="44" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -1977,7 +1977,7 @@
       </c>
       <c r="I44" s="15" t="n">
         <f aca="false">IF(B44="","",MAX(0,B44-$B$6))</f>
-        <v>999428385</v>
+        <v>995185690</v>
       </c>
     </row>
     <row r="45" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -2005,7 +2005,7 @@
       </c>
       <c r="I45" s="15" t="n">
         <f aca="false">IF(B45="","",MAX(0,B45-$B$6))</f>
-        <v>1199428385</v>
+        <v>1195185690</v>
       </c>
     </row>
     <row r="46" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -2033,7 +2033,7 @@
       </c>
       <c r="I46" s="15" t="n">
         <f aca="false">IF(B46="","",MAX(0,B46-$B$6))</f>
-        <v>1399428385</v>
+        <v>1395185690</v>
       </c>
     </row>
     <row r="47" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -2061,7 +2061,7 @@
       </c>
       <c r="I47" s="15" t="n">
         <f aca="false">IF(B47="","",MAX(0,B47-$B$6))</f>
-        <v>1599428385</v>
+        <v>1595185690</v>
       </c>
     </row>
     <row r="48" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -2089,7 +2089,7 @@
       </c>
       <c r="I48" s="15" t="n">
         <f aca="false">IF(B48="","",MAX(0,B48-$B$6))</f>
-        <v>1799428385</v>
+        <v>1795185690</v>
       </c>
     </row>
     <row r="49" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -2117,7 +2117,7 @@
       </c>
       <c r="I49" s="15" t="n">
         <f aca="false">IF(B49="","",MAX(0,B49-$B$6))</f>
-        <v>1999428385</v>
+        <v>1995185690</v>
       </c>
     </row>
     <row r="50" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -2145,7 +2145,7 @@
       </c>
       <c r="I50" s="15" t="n">
         <f aca="false">IF(B50="","",MAX(0,B50-$B$6))</f>
-        <v>2199428385</v>
+        <v>2195185690</v>
       </c>
     </row>
     <row r="51" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -2173,7 +2173,7 @@
       </c>
       <c r="I51" s="15" t="n">
         <f aca="false">IF(B51="","",MAX(0,B51-$B$6))</f>
-        <v>2399428385</v>
+        <v>2395185690</v>
       </c>
     </row>
     <row r="52" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -2201,7 +2201,7 @@
       </c>
       <c r="I52" s="15" t="n">
         <f aca="false">IF(B52="","",MAX(0,B52-$B$6))</f>
-        <v>2599428385</v>
+        <v>2595185690</v>
       </c>
     </row>
     <row r="53" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -2229,7 +2229,7 @@
       </c>
       <c r="I53" s="15" t="n">
         <f aca="false">IF(B53="","",MAX(0,B53-$B$6))</f>
-        <v>2799428385</v>
+        <v>2795185690</v>
       </c>
     </row>
     <row r="54" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -2257,7 +2257,7 @@
       </c>
       <c r="I54" s="15" t="n">
         <f aca="false">IF(B54="","",MAX(0,B54-$B$6))</f>
-        <v>2999428385</v>
+        <v>2995185690</v>
       </c>
     </row>
     <row r="56" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -2388,18 +2388,18 @@
         <v>500000000</v>
       </c>
       <c r="E6" s="11" t="n">
-        <v>159025315</v>
+        <v>163268010</v>
       </c>
       <c r="F6" s="15" t="n">
         <f aca="false">IF(ISNUMBER(D6),MAX(0,D6-N(E6)),"")</f>
-        <v>340974685</v>
+        <v>336731990</v>
       </c>
       <c r="G6" s="11" t="n">
-        <v>9650000</v>
+        <v>8240000</v>
       </c>
       <c r="H6" s="15" t="n">
         <f aca="false">IF(ISNUMBER(D6),MIN(N(G6)*N(C6),N(F6)),N(G6)*N(C6))</f>
-        <v>9650000</v>
+        <v>8240000</v>
       </c>
       <c r="I6" s="16" t="s">
         <v>91</v>
@@ -3061,7 +3061,7 @@
       </c>
       <c r="B32" s="7" t="n">
         <f aca="false">SUM(E5:E30)</f>
-        <v>405026815</v>
+        <v>409269510</v>
       </c>
     </row>
     <row r="33" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -3079,7 +3079,7 @@
       </c>
       <c r="B34" s="7" t="n">
         <f aca="false">'Iso Fest'!B6</f>
-        <v>500571615</v>
+        <v>504814310</v>
       </c>
     </row>
     <row r="35" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -3088,7 +3088,7 @@
       </c>
       <c r="B35" s="7" t="n">
         <f aca="false">SUM(H5:H30)</f>
-        <v>10805000</v>
+        <v>9395000</v>
       </c>
     </row>
     <row r="36" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -3097,7 +3097,7 @@
       </c>
       <c r="B36" s="7" t="n">
         <f aca="false">B34+B35</f>
-        <v>511376615</v>
+        <v>514209310</v>
       </c>
     </row>
     <row r="37" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -3115,7 +3115,7 @@
       </c>
       <c r="B38" s="7" t="n">
         <f aca="false">MAX(0,INDEX('Iso Fest'!B13:B54,'Iso Fest'!B9)-B36)</f>
-        <v>88623385</v>
+        <v>85790690</v>
       </c>
     </row>
     <row r="40" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">

--- a/Iso_Fest_Tracker.xlsx
+++ b/Iso_Fest_Tracker.xlsx
@@ -960,7 +960,7 @@
         <v>9</v>
       </c>
       <c r="B6" s="6" t="n">
-        <v>504814310</v>
+        <v>506918910</v>
       </c>
       <c r="D6" s="4" t="s">
         <v>10</v>
@@ -1008,7 +1008,7 @@
       </c>
       <c r="B8" s="7" t="n">
         <f aca="false">IFERROR(INDEX(I13:I54,MATCH(TRUE(),INDEX(B13:B54&gt;B6,0),0)),0)</f>
-        <v>20185690</v>
+        <v>18081090</v>
       </c>
     </row>
     <row r="9" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -1023,7 +1023,7 @@
       </c>
       <c r="G9" s="7" t="n">
         <f aca="false">Scoring!B36</f>
-        <v>514209310</v>
+        <v>516313910</v>
       </c>
     </row>
     <row r="10" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -1032,7 +1032,7 @@
       </c>
       <c r="B10" s="7" t="n">
         <f aca="false">MAX(0,INDEX(B13:B54,B9)-B6)</f>
-        <v>95185690</v>
+        <v>93081090</v>
       </c>
       <c r="D10" s="3" t="s">
         <v>17</v>
@@ -1048,7 +1048,7 @@
       </c>
       <c r="B11" s="7" t="n">
         <f aca="true">IFERROR(B10/MAX(B5-NOW(),0.01),0)</f>
-        <v>29028374.8208475</v>
+        <v>28440993.9446738</v>
       </c>
     </row>
     <row r="12" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -1745,7 +1745,7 @@
       </c>
       <c r="I36" s="15" t="n">
         <f aca="false">IF(B36="","",MAX(0,B36-$B$6))</f>
-        <v>20185690</v>
+        <v>18081090</v>
       </c>
     </row>
     <row r="37" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -1775,7 +1775,7 @@
       </c>
       <c r="I37" s="15" t="n">
         <f aca="false">IF(B37="","",MAX(0,B37-$B$6))</f>
-        <v>45185690</v>
+        <v>43081090</v>
       </c>
     </row>
     <row r="38" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -1803,7 +1803,7 @@
       </c>
       <c r="I38" s="15" t="n">
         <f aca="false">IF(B38="","",MAX(0,B38-$B$6))</f>
-        <v>95185690</v>
+        <v>93081090</v>
       </c>
     </row>
     <row r="39" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -1833,7 +1833,7 @@
       </c>
       <c r="I39" s="15" t="n">
         <f aca="false">IF(B39="","",MAX(0,B39-$B$6))</f>
-        <v>145185690</v>
+        <v>143081090</v>
       </c>
     </row>
     <row r="40" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -1861,7 +1861,7 @@
       </c>
       <c r="I40" s="15" t="n">
         <f aca="false">IF(B40="","",MAX(0,B40-$B$6))</f>
-        <v>245185690</v>
+        <v>243081090</v>
       </c>
     </row>
     <row r="41" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -1891,7 +1891,7 @@
       </c>
       <c r="I41" s="15" t="n">
         <f aca="false">IF(B41="","",MAX(0,B41-$B$6))</f>
-        <v>395185690</v>
+        <v>393081090</v>
       </c>
     </row>
     <row r="42" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -1919,7 +1919,7 @@
       </c>
       <c r="I42" s="15" t="n">
         <f aca="false">IF(B42="","",MAX(0,B42-$B$6))</f>
-        <v>595185690</v>
+        <v>593081090</v>
       </c>
     </row>
     <row r="43" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -1949,7 +1949,7 @@
       </c>
       <c r="I43" s="15" t="n">
         <f aca="false">IF(B43="","",MAX(0,B43-$B$6))</f>
-        <v>795185690</v>
+        <v>793081090</v>
       </c>
     </row>
     <row r="44" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -1977,7 +1977,7 @@
       </c>
       <c r="I44" s="15" t="n">
         <f aca="false">IF(B44="","",MAX(0,B44-$B$6))</f>
-        <v>995185690</v>
+        <v>993081090</v>
       </c>
     </row>
     <row r="45" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -2005,7 +2005,7 @@
       </c>
       <c r="I45" s="15" t="n">
         <f aca="false">IF(B45="","",MAX(0,B45-$B$6))</f>
-        <v>1195185690</v>
+        <v>1193081090</v>
       </c>
     </row>
     <row r="46" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -2033,7 +2033,7 @@
       </c>
       <c r="I46" s="15" t="n">
         <f aca="false">IF(B46="","",MAX(0,B46-$B$6))</f>
-        <v>1395185690</v>
+        <v>1393081090</v>
       </c>
     </row>
     <row r="47" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -2061,7 +2061,7 @@
       </c>
       <c r="I47" s="15" t="n">
         <f aca="false">IF(B47="","",MAX(0,B47-$B$6))</f>
-        <v>1595185690</v>
+        <v>1593081090</v>
       </c>
     </row>
     <row r="48" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -2089,7 +2089,7 @@
       </c>
       <c r="I48" s="15" t="n">
         <f aca="false">IF(B48="","",MAX(0,B48-$B$6))</f>
-        <v>1795185690</v>
+        <v>1793081090</v>
       </c>
     </row>
     <row r="49" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -2117,7 +2117,7 @@
       </c>
       <c r="I49" s="15" t="n">
         <f aca="false">IF(B49="","",MAX(0,B49-$B$6))</f>
-        <v>1995185690</v>
+        <v>1993081090</v>
       </c>
     </row>
     <row r="50" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -2145,7 +2145,7 @@
       </c>
       <c r="I50" s="15" t="n">
         <f aca="false">IF(B50="","",MAX(0,B50-$B$6))</f>
-        <v>2195185690</v>
+        <v>2193081090</v>
       </c>
     </row>
     <row r="51" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -2173,7 +2173,7 @@
       </c>
       <c r="I51" s="15" t="n">
         <f aca="false">IF(B51="","",MAX(0,B51-$B$6))</f>
-        <v>2395185690</v>
+        <v>2393081090</v>
       </c>
     </row>
     <row r="52" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -2201,7 +2201,7 @@
       </c>
       <c r="I52" s="15" t="n">
         <f aca="false">IF(B52="","",MAX(0,B52-$B$6))</f>
-        <v>2595185690</v>
+        <v>2593081090</v>
       </c>
     </row>
     <row r="53" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -2229,7 +2229,7 @@
       </c>
       <c r="I53" s="15" t="n">
         <f aca="false">IF(B53="","",MAX(0,B53-$B$6))</f>
-        <v>2795185690</v>
+        <v>2793081090</v>
       </c>
     </row>
     <row r="54" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -2257,7 +2257,7 @@
       </c>
       <c r="I54" s="15" t="n">
         <f aca="false">IF(B54="","",MAX(0,B54-$B$6))</f>
-        <v>2995185690</v>
+        <v>2993081090</v>
       </c>
     </row>
     <row r="56" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -3070,7 +3070,7 @@
       </c>
       <c r="B33" s="7" t="n">
         <f aca="false">'Iso Fest'!B6-B32</f>
-        <v>95544800</v>
+        <v>97649400</v>
       </c>
     </row>
     <row r="34" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -3079,7 +3079,7 @@
       </c>
       <c r="B34" s="7" t="n">
         <f aca="false">'Iso Fest'!B6</f>
-        <v>504814310</v>
+        <v>506918910</v>
       </c>
     </row>
     <row r="35" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -3097,7 +3097,7 @@
       </c>
       <c r="B36" s="7" t="n">
         <f aca="false">B34+B35</f>
-        <v>514209310</v>
+        <v>516313910</v>
       </c>
     </row>
     <row r="37" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -3115,7 +3115,7 @@
       </c>
       <c r="B38" s="7" t="n">
         <f aca="false">MAX(0,INDEX('Iso Fest'!B13:B54,'Iso Fest'!B9)-B36)</f>
-        <v>85790690</v>
+        <v>83686090</v>
       </c>
     </row>
     <row r="40" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">

--- a/Iso_Fest_Tracker.xlsx
+++ b/Iso_Fest_Tracker.xlsx
@@ -960,7 +960,7 @@
         <v>9</v>
       </c>
       <c r="B6" s="6" t="n">
-        <v>506918910</v>
+        <v>507168910</v>
       </c>
       <c r="D6" s="4" t="s">
         <v>10</v>
@@ -1008,7 +1008,7 @@
       </c>
       <c r="B8" s="7" t="n">
         <f aca="false">IFERROR(INDEX(I13:I54,MATCH(TRUE(),INDEX(B13:B54&gt;B6,0),0)),0)</f>
-        <v>18081090</v>
+        <v>17831090</v>
       </c>
     </row>
     <row r="9" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -1023,7 +1023,7 @@
       </c>
       <c r="G9" s="7" t="n">
         <f aca="false">Scoring!B36</f>
-        <v>516313910</v>
+        <v>516563910</v>
       </c>
     </row>
     <row r="10" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -1032,7 +1032,7 @@
       </c>
       <c r="B10" s="7" t="n">
         <f aca="false">MAX(0,INDEX(B13:B54,B9)-B6)</f>
-        <v>93081090</v>
+        <v>92831090</v>
       </c>
       <c r="D10" s="3" t="s">
         <v>17</v>
@@ -1048,7 +1048,7 @@
       </c>
       <c r="B11" s="7" t="n">
         <f aca="true">IFERROR(B10/MAX(B5-NOW(),0.01),0)</f>
-        <v>28440993.9446738</v>
+        <v>30022418.391075</v>
       </c>
     </row>
     <row r="12" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -1745,7 +1745,7 @@
       </c>
       <c r="I36" s="15" t="n">
         <f aca="false">IF(B36="","",MAX(0,B36-$B$6))</f>
-        <v>18081090</v>
+        <v>17831090</v>
       </c>
     </row>
     <row r="37" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -1775,7 +1775,7 @@
       </c>
       <c r="I37" s="15" t="n">
         <f aca="false">IF(B37="","",MAX(0,B37-$B$6))</f>
-        <v>43081090</v>
+        <v>42831090</v>
       </c>
     </row>
     <row r="38" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -1803,7 +1803,7 @@
       </c>
       <c r="I38" s="15" t="n">
         <f aca="false">IF(B38="","",MAX(0,B38-$B$6))</f>
-        <v>93081090</v>
+        <v>92831090</v>
       </c>
     </row>
     <row r="39" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -1833,7 +1833,7 @@
       </c>
       <c r="I39" s="15" t="n">
         <f aca="false">IF(B39="","",MAX(0,B39-$B$6))</f>
-        <v>143081090</v>
+        <v>142831090</v>
       </c>
     </row>
     <row r="40" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -1861,7 +1861,7 @@
       </c>
       <c r="I40" s="15" t="n">
         <f aca="false">IF(B40="","",MAX(0,B40-$B$6))</f>
-        <v>243081090</v>
+        <v>242831090</v>
       </c>
     </row>
     <row r="41" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -1891,7 +1891,7 @@
       </c>
       <c r="I41" s="15" t="n">
         <f aca="false">IF(B41="","",MAX(0,B41-$B$6))</f>
-        <v>393081090</v>
+        <v>392831090</v>
       </c>
     </row>
     <row r="42" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -1919,7 +1919,7 @@
       </c>
       <c r="I42" s="15" t="n">
         <f aca="false">IF(B42="","",MAX(0,B42-$B$6))</f>
-        <v>593081090</v>
+        <v>592831090</v>
       </c>
     </row>
     <row r="43" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -1949,7 +1949,7 @@
       </c>
       <c r="I43" s="15" t="n">
         <f aca="false">IF(B43="","",MAX(0,B43-$B$6))</f>
-        <v>793081090</v>
+        <v>792831090</v>
       </c>
     </row>
     <row r="44" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -1977,7 +1977,7 @@
       </c>
       <c r="I44" s="15" t="n">
         <f aca="false">IF(B44="","",MAX(0,B44-$B$6))</f>
-        <v>993081090</v>
+        <v>992831090</v>
       </c>
     </row>
     <row r="45" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -2005,7 +2005,7 @@
       </c>
       <c r="I45" s="15" t="n">
         <f aca="false">IF(B45="","",MAX(0,B45-$B$6))</f>
-        <v>1193081090</v>
+        <v>1192831090</v>
       </c>
     </row>
     <row r="46" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -2033,7 +2033,7 @@
       </c>
       <c r="I46" s="15" t="n">
         <f aca="false">IF(B46="","",MAX(0,B46-$B$6))</f>
-        <v>1393081090</v>
+        <v>1392831090</v>
       </c>
     </row>
     <row r="47" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -2061,7 +2061,7 @@
       </c>
       <c r="I47" s="15" t="n">
         <f aca="false">IF(B47="","",MAX(0,B47-$B$6))</f>
-        <v>1593081090</v>
+        <v>1592831090</v>
       </c>
     </row>
     <row r="48" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -2089,7 +2089,7 @@
       </c>
       <c r="I48" s="15" t="n">
         <f aca="false">IF(B48="","",MAX(0,B48-$B$6))</f>
-        <v>1793081090</v>
+        <v>1792831090</v>
       </c>
     </row>
     <row r="49" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -2117,7 +2117,7 @@
       </c>
       <c r="I49" s="15" t="n">
         <f aca="false">IF(B49="","",MAX(0,B49-$B$6))</f>
-        <v>1993081090</v>
+        <v>1992831090</v>
       </c>
     </row>
     <row r="50" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -2145,7 +2145,7 @@
       </c>
       <c r="I50" s="15" t="n">
         <f aca="false">IF(B50="","",MAX(0,B50-$B$6))</f>
-        <v>2193081090</v>
+        <v>2192831090</v>
       </c>
     </row>
     <row r="51" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -2173,7 +2173,7 @@
       </c>
       <c r="I51" s="15" t="n">
         <f aca="false">IF(B51="","",MAX(0,B51-$B$6))</f>
-        <v>2393081090</v>
+        <v>2392831090</v>
       </c>
     </row>
     <row r="52" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -2201,7 +2201,7 @@
       </c>
       <c r="I52" s="15" t="n">
         <f aca="false">IF(B52="","",MAX(0,B52-$B$6))</f>
-        <v>2593081090</v>
+        <v>2592831090</v>
       </c>
     </row>
     <row r="53" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -2229,7 +2229,7 @@
       </c>
       <c r="I53" s="15" t="n">
         <f aca="false">IF(B53="","",MAX(0,B53-$B$6))</f>
-        <v>2793081090</v>
+        <v>2792831090</v>
       </c>
     </row>
     <row r="54" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -2257,7 +2257,7 @@
       </c>
       <c r="I54" s="15" t="n">
         <f aca="false">IF(B54="","",MAX(0,B54-$B$6))</f>
-        <v>2993081090</v>
+        <v>2992831090</v>
       </c>
     </row>
     <row r="56" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -2419,11 +2419,11 @@
         <v>250000000</v>
       </c>
       <c r="E7" s="11" t="n">
-        <v>10500000</v>
+        <v>10750000</v>
       </c>
       <c r="F7" s="15" t="n">
         <f aca="false">IF(ISNUMBER(D7),MAX(0,D7-N(E7)),"")</f>
-        <v>239500000</v>
+        <v>239250000</v>
       </c>
       <c r="G7" s="11"/>
       <c r="H7" s="15" t="n">
@@ -3061,7 +3061,7 @@
       </c>
       <c r="B32" s="7" t="n">
         <f aca="false">SUM(E5:E30)</f>
-        <v>409269510</v>
+        <v>409519510</v>
       </c>
     </row>
     <row r="33" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -3079,7 +3079,7 @@
       </c>
       <c r="B34" s="7" t="n">
         <f aca="false">'Iso Fest'!B6</f>
-        <v>506918910</v>
+        <v>507168910</v>
       </c>
     </row>
     <row r="35" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -3097,7 +3097,7 @@
       </c>
       <c r="B36" s="7" t="n">
         <f aca="false">B34+B35</f>
-        <v>516313910</v>
+        <v>516563910</v>
       </c>
     </row>
     <row r="37" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -3115,7 +3115,7 @@
       </c>
       <c r="B38" s="7" t="n">
         <f aca="false">MAX(0,INDEX('Iso Fest'!B13:B54,'Iso Fest'!B9)-B36)</f>
-        <v>83686090</v>
+        <v>83436090</v>
       </c>
     </row>
     <row r="40" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">

--- a/Iso_Fest_Tracker.xlsx
+++ b/Iso_Fest_Tracker.xlsx
@@ -188,10 +188,10 @@
     <t xml:space="preserve">Professor Xavier to 6 red stars</t>
   </si>
   <si>
+    <t xml:space="preserve">Maestro to 6 red stars</t>
+  </si>
+  <si>
     <t xml:space="preserve">Not claimed</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Maestro to 6 red stars</t>
   </si>
   <si>
     <t xml:space="preserve">Knull to 7 red stars</t>
@@ -960,7 +960,7 @@
         <v>9</v>
       </c>
       <c r="B6" s="6" t="n">
-        <v>507168910</v>
+        <v>518436290</v>
       </c>
       <c r="D6" s="4" t="s">
         <v>10</v>
@@ -971,11 +971,11 @@
       </c>
       <c r="F6" s="7" t="n">
         <f aca="false">SUMPRODUCT((A13:A54&lt;=$B$9)*(H13:H54&lt;&gt;"Claimed")*F13:F54)</f>
-        <v>5600000</v>
+        <v>4200000</v>
       </c>
       <c r="G6" s="7" t="n">
         <f aca="false">SUMPRODUCT((A13:A54&lt;=$B$9)*(H13:H54&lt;&gt;"Claimed")*G13:G54)</f>
-        <v>7700000</v>
+        <v>5800000</v>
       </c>
     </row>
     <row r="7" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -995,11 +995,11 @@
       </c>
       <c r="F7" s="7" t="n">
         <f aca="false">SUMPRODUCT((B13:B54&lt;&gt;"")*(B13:B54&lt;=$B$6)*(H13:H54&lt;&gt;"Claimed")*F13:F54)</f>
-        <v>1400000</v>
+        <v>0</v>
       </c>
       <c r="G7" s="7" t="n">
         <f aca="false">SUMPRODUCT((B13:B54&lt;&gt;"")*(B13:B54&lt;=$B$6)*(H13:H54&lt;&gt;"Claimed")*G13:G54)</f>
-        <v>1900000</v>
+        <v>0</v>
       </c>
     </row>
     <row r="8" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -1008,7 +1008,7 @@
       </c>
       <c r="B8" s="7" t="n">
         <f aca="false">IFERROR(INDEX(I13:I54,MATCH(TRUE(),INDEX(B13:B54&gt;B6,0),0)),0)</f>
-        <v>17831090</v>
+        <v>6563710</v>
       </c>
     </row>
     <row r="9" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -1023,7 +1023,7 @@
       </c>
       <c r="G9" s="7" t="n">
         <f aca="false">Scoring!B36</f>
-        <v>516563910</v>
+        <v>527831290</v>
       </c>
     </row>
     <row r="10" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -1032,14 +1032,14 @@
       </c>
       <c r="B10" s="7" t="n">
         <f aca="false">MAX(0,INDEX(B13:B54,B9)-B6)</f>
-        <v>92831090</v>
+        <v>81563710</v>
       </c>
       <c r="D10" s="3" t="s">
         <v>17</v>
       </c>
       <c r="G10" s="7" t="n">
         <f aca="false">Scoring!B37</f>
-        <v>23</v>
+        <v>24</v>
       </c>
     </row>
     <row r="11" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -1048,7 +1048,7 @@
       </c>
       <c r="B11" s="7" t="n">
         <f aca="true">IFERROR(B10/MAX(B5-NOW(),0.01),0)</f>
-        <v>30022418.391075</v>
+        <v>27453364.4869936</v>
       </c>
     </row>
     <row r="12" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -1713,7 +1713,7 @@
         <v>1900000</v>
       </c>
       <c r="H35" s="14" t="s">
-        <v>55</v>
+        <v>26</v>
       </c>
       <c r="I35" s="15" t="n">
         <f aca="false">IF(B35="","",MAX(0,B35-$B$6))</f>
@@ -1728,7 +1728,7 @@
         <v>525000000</v>
       </c>
       <c r="C36" s="12" t="s">
-        <v>56</v>
+        <v>55</v>
       </c>
       <c r="D36" s="12"/>
       <c r="E36" s="13" t="n">
@@ -1741,11 +1741,11 @@
         <v>1900000</v>
       </c>
       <c r="H36" s="14" t="s">
-        <v>55</v>
+        <v>56</v>
       </c>
       <c r="I36" s="15" t="n">
         <f aca="false">IF(B36="","",MAX(0,B36-$B$6))</f>
-        <v>17831090</v>
+        <v>6563710</v>
       </c>
     </row>
     <row r="37" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -1771,11 +1771,11 @@
         <v>1900000</v>
       </c>
       <c r="H37" s="14" t="s">
-        <v>55</v>
+        <v>56</v>
       </c>
       <c r="I37" s="15" t="n">
         <f aca="false">IF(B37="","",MAX(0,B37-$B$6))</f>
-        <v>42831090</v>
+        <v>31563710</v>
       </c>
     </row>
     <row r="38" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -1799,11 +1799,11 @@
         <v>2000000</v>
       </c>
       <c r="H38" s="14" t="s">
-        <v>55</v>
+        <v>56</v>
       </c>
       <c r="I38" s="15" t="n">
         <f aca="false">IF(B38="","",MAX(0,B38-$B$6))</f>
-        <v>92831090</v>
+        <v>81563710</v>
       </c>
     </row>
     <row r="39" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -1829,11 +1829,11 @@
         <v>2000000</v>
       </c>
       <c r="H39" s="14" t="s">
-        <v>55</v>
+        <v>56</v>
       </c>
       <c r="I39" s="15" t="n">
         <f aca="false">IF(B39="","",MAX(0,B39-$B$6))</f>
-        <v>142831090</v>
+        <v>131563710</v>
       </c>
     </row>
     <row r="40" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -1857,11 +1857,11 @@
         <v>2000000</v>
       </c>
       <c r="H40" s="14" t="s">
-        <v>55</v>
+        <v>56</v>
       </c>
       <c r="I40" s="15" t="n">
         <f aca="false">IF(B40="","",MAX(0,B40-$B$6))</f>
-        <v>242831090</v>
+        <v>231563710</v>
       </c>
     </row>
     <row r="41" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -1887,11 +1887,11 @@
         <v>2000000</v>
       </c>
       <c r="H41" s="14" t="s">
-        <v>55</v>
+        <v>56</v>
       </c>
       <c r="I41" s="15" t="n">
         <f aca="false">IF(B41="","",MAX(0,B41-$B$6))</f>
-        <v>392831090</v>
+        <v>381563710</v>
       </c>
     </row>
     <row r="42" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -1915,11 +1915,11 @@
         <v>2000000</v>
       </c>
       <c r="H42" s="14" t="s">
-        <v>55</v>
+        <v>56</v>
       </c>
       <c r="I42" s="15" t="n">
         <f aca="false">IF(B42="","",MAX(0,B42-$B$6))</f>
-        <v>592831090</v>
+        <v>581563710</v>
       </c>
     </row>
     <row r="43" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -1945,11 +1945,11 @@
         <v>2000000</v>
       </c>
       <c r="H43" s="14" t="s">
-        <v>55</v>
+        <v>56</v>
       </c>
       <c r="I43" s="15" t="n">
         <f aca="false">IF(B43="","",MAX(0,B43-$B$6))</f>
-        <v>792831090</v>
+        <v>781563710</v>
       </c>
     </row>
     <row r="44" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -1973,11 +1973,11 @@
         <v>2700000</v>
       </c>
       <c r="H44" s="14" t="s">
-        <v>55</v>
+        <v>56</v>
       </c>
       <c r="I44" s="15" t="n">
         <f aca="false">IF(B44="","",MAX(0,B44-$B$6))</f>
-        <v>992831090</v>
+        <v>981563710</v>
       </c>
     </row>
     <row r="45" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -2001,11 +2001,11 @@
         <v>2700000</v>
       </c>
       <c r="H45" s="14" t="s">
-        <v>55</v>
+        <v>56</v>
       </c>
       <c r="I45" s="15" t="n">
         <f aca="false">IF(B45="","",MAX(0,B45-$B$6))</f>
-        <v>1192831090</v>
+        <v>1181563710</v>
       </c>
     </row>
     <row r="46" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -2029,11 +2029,11 @@
         <v>2700000</v>
       </c>
       <c r="H46" s="14" t="s">
-        <v>55</v>
+        <v>56</v>
       </c>
       <c r="I46" s="15" t="n">
         <f aca="false">IF(B46="","",MAX(0,B46-$B$6))</f>
-        <v>1392831090</v>
+        <v>1381563710</v>
       </c>
     </row>
     <row r="47" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -2057,11 +2057,11 @@
         <v>2700000</v>
       </c>
       <c r="H47" s="14" t="s">
-        <v>55</v>
+        <v>56</v>
       </c>
       <c r="I47" s="15" t="n">
         <f aca="false">IF(B47="","",MAX(0,B47-$B$6))</f>
-        <v>1592831090</v>
+        <v>1581563710</v>
       </c>
     </row>
     <row r="48" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -2085,11 +2085,11 @@
         <v>2700000</v>
       </c>
       <c r="H48" s="14" t="s">
-        <v>55</v>
+        <v>56</v>
       </c>
       <c r="I48" s="15" t="n">
         <f aca="false">IF(B48="","",MAX(0,B48-$B$6))</f>
-        <v>1792831090</v>
+        <v>1781563710</v>
       </c>
     </row>
     <row r="49" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -2113,11 +2113,11 @@
         <v>2700000</v>
       </c>
       <c r="H49" s="14" t="s">
-        <v>55</v>
+        <v>56</v>
       </c>
       <c r="I49" s="15" t="n">
         <f aca="false">IF(B49="","",MAX(0,B49-$B$6))</f>
-        <v>1992831090</v>
+        <v>1981563710</v>
       </c>
     </row>
     <row r="50" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -2141,11 +2141,11 @@
         <v>2700000</v>
       </c>
       <c r="H50" s="14" t="s">
-        <v>55</v>
+        <v>56</v>
       </c>
       <c r="I50" s="15" t="n">
         <f aca="false">IF(B50="","",MAX(0,B50-$B$6))</f>
-        <v>2192831090</v>
+        <v>2181563710</v>
       </c>
     </row>
     <row r="51" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -2169,11 +2169,11 @@
         <v>2700000</v>
       </c>
       <c r="H51" s="14" t="s">
-        <v>55</v>
+        <v>56</v>
       </c>
       <c r="I51" s="15" t="n">
         <f aca="false">IF(B51="","",MAX(0,B51-$B$6))</f>
-        <v>2392831090</v>
+        <v>2381563710</v>
       </c>
     </row>
     <row r="52" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -2197,11 +2197,11 @@
         <v>2700000</v>
       </c>
       <c r="H52" s="14" t="s">
-        <v>55</v>
+        <v>56</v>
       </c>
       <c r="I52" s="15" t="n">
         <f aca="false">IF(B52="","",MAX(0,B52-$B$6))</f>
-        <v>2592831090</v>
+        <v>2581563710</v>
       </c>
     </row>
     <row r="53" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -2225,11 +2225,11 @@
         <v>2700000</v>
       </c>
       <c r="H53" s="14" t="s">
-        <v>55</v>
+        <v>56</v>
       </c>
       <c r="I53" s="15" t="n">
         <f aca="false">IF(B53="","",MAX(0,B53-$B$6))</f>
-        <v>2792831090</v>
+        <v>2781563710</v>
       </c>
     </row>
     <row r="54" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -2253,11 +2253,11 @@
         <v>2700000</v>
       </c>
       <c r="H54" s="14" t="s">
-        <v>55</v>
+        <v>56</v>
       </c>
       <c r="I54" s="15" t="n">
         <f aca="false">IF(B54="","",MAX(0,B54-$B$6))</f>
-        <v>2992831090</v>
+        <v>2981563710</v>
       </c>
     </row>
     <row r="56" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -2359,11 +2359,11 @@
         <v>51000000</v>
       </c>
       <c r="E5" s="11" t="n">
-        <v>39000000</v>
+        <v>45000000</v>
       </c>
       <c r="F5" s="15" t="n">
         <f aca="false">IF(ISNUMBER(D5),MAX(0,D5-N(E5)),"")</f>
-        <v>12000000</v>
+        <v>6000000</v>
       </c>
       <c r="G5" s="11"/>
       <c r="H5" s="15" t="n">
@@ -2388,11 +2388,11 @@
         <v>500000000</v>
       </c>
       <c r="E6" s="11" t="n">
-        <v>163268010</v>
+        <v>168895390</v>
       </c>
       <c r="F6" s="15" t="n">
         <f aca="false">IF(ISNUMBER(D6),MAX(0,D6-N(E6)),"")</f>
-        <v>336731990</v>
+        <v>331104610</v>
       </c>
       <c r="G6" s="11" t="n">
         <v>8240000</v>
@@ -3061,7 +3061,7 @@
       </c>
       <c r="B32" s="7" t="n">
         <f aca="false">SUM(E5:E30)</f>
-        <v>409519510</v>
+        <v>421146890</v>
       </c>
     </row>
     <row r="33" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -3070,7 +3070,7 @@
       </c>
       <c r="B33" s="7" t="n">
         <f aca="false">'Iso Fest'!B6-B32</f>
-        <v>97649400</v>
+        <v>97289400</v>
       </c>
     </row>
     <row r="34" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -3079,7 +3079,7 @@
       </c>
       <c r="B34" s="7" t="n">
         <f aca="false">'Iso Fest'!B6</f>
-        <v>507168910</v>
+        <v>518436290</v>
       </c>
     </row>
     <row r="35" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -3097,7 +3097,7 @@
       </c>
       <c r="B36" s="7" t="n">
         <f aca="false">B34+B35</f>
-        <v>516563910</v>
+        <v>527831290</v>
       </c>
     </row>
     <row r="37" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -3106,7 +3106,7 @@
       </c>
       <c r="B37" s="7" t="n">
         <f aca="false">IFERROR(INDEX('Iso Fest'!A13:A54,MATCH(B36,'Iso Fest'!B13:B54,1)),"Below milestone 15")</f>
-        <v>23</v>
+        <v>24</v>
       </c>
     </row>
     <row r="38" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -3115,7 +3115,7 @@
       </c>
       <c r="B38" s="7" t="n">
         <f aca="false">MAX(0,INDEX('Iso Fest'!B13:B54,'Iso Fest'!B9)-B36)</f>
-        <v>83436090</v>
+        <v>72168710</v>
       </c>
     </row>
     <row r="40" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">

--- a/Iso_Fest_Tracker.xlsx
+++ b/Iso_Fest_Tracker.xlsx
@@ -960,7 +960,7 @@
         <v>9</v>
       </c>
       <c r="B6" s="6" t="n">
-        <v>518436290</v>
+        <v>521086290</v>
       </c>
       <c r="D6" s="4" t="s">
         <v>10</v>
@@ -1008,7 +1008,7 @@
       </c>
       <c r="B8" s="7" t="n">
         <f aca="false">IFERROR(INDEX(I13:I54,MATCH(TRUE(),INDEX(B13:B54&gt;B6,0),0)),0)</f>
-        <v>6563710</v>
+        <v>3913710</v>
       </c>
     </row>
     <row r="9" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -1023,7 +1023,7 @@
       </c>
       <c r="G9" s="7" t="n">
         <f aca="false">Scoring!B36</f>
-        <v>527831290</v>
+        <v>530481290</v>
       </c>
     </row>
     <row r="10" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -1032,7 +1032,7 @@
       </c>
       <c r="B10" s="7" t="n">
         <f aca="false">MAX(0,INDEX(B13:B54,B9)-B6)</f>
-        <v>81563710</v>
+        <v>78913710</v>
       </c>
       <c r="D10" s="3" t="s">
         <v>17</v>
@@ -1048,7 +1048,7 @@
       </c>
       <c r="B11" s="7" t="n">
         <f aca="true">IFERROR(B10/MAX(B5-NOW(),0.01),0)</f>
-        <v>27453364.4869936</v>
+        <v>27986210.7267684</v>
       </c>
     </row>
     <row r="12" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -1745,7 +1745,7 @@
       </c>
       <c r="I36" s="15" t="n">
         <f aca="false">IF(B36="","",MAX(0,B36-$B$6))</f>
-        <v>6563710</v>
+        <v>3913710</v>
       </c>
     </row>
     <row r="37" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -1775,7 +1775,7 @@
       </c>
       <c r="I37" s="15" t="n">
         <f aca="false">IF(B37="","",MAX(0,B37-$B$6))</f>
-        <v>31563710</v>
+        <v>28913710</v>
       </c>
     </row>
     <row r="38" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -1803,7 +1803,7 @@
       </c>
       <c r="I38" s="15" t="n">
         <f aca="false">IF(B38="","",MAX(0,B38-$B$6))</f>
-        <v>81563710</v>
+        <v>78913710</v>
       </c>
     </row>
     <row r="39" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -1833,7 +1833,7 @@
       </c>
       <c r="I39" s="15" t="n">
         <f aca="false">IF(B39="","",MAX(0,B39-$B$6))</f>
-        <v>131563710</v>
+        <v>128913710</v>
       </c>
     </row>
     <row r="40" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -1861,7 +1861,7 @@
       </c>
       <c r="I40" s="15" t="n">
         <f aca="false">IF(B40="","",MAX(0,B40-$B$6))</f>
-        <v>231563710</v>
+        <v>228913710</v>
       </c>
     </row>
     <row r="41" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -1891,7 +1891,7 @@
       </c>
       <c r="I41" s="15" t="n">
         <f aca="false">IF(B41="","",MAX(0,B41-$B$6))</f>
-        <v>381563710</v>
+        <v>378913710</v>
       </c>
     </row>
     <row r="42" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -1919,7 +1919,7 @@
       </c>
       <c r="I42" s="15" t="n">
         <f aca="false">IF(B42="","",MAX(0,B42-$B$6))</f>
-        <v>581563710</v>
+        <v>578913710</v>
       </c>
     </row>
     <row r="43" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -1949,7 +1949,7 @@
       </c>
       <c r="I43" s="15" t="n">
         <f aca="false">IF(B43="","",MAX(0,B43-$B$6))</f>
-        <v>781563710</v>
+        <v>778913710</v>
       </c>
     </row>
     <row r="44" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -1977,7 +1977,7 @@
       </c>
       <c r="I44" s="15" t="n">
         <f aca="false">IF(B44="","",MAX(0,B44-$B$6))</f>
-        <v>981563710</v>
+        <v>978913710</v>
       </c>
     </row>
     <row r="45" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -2005,7 +2005,7 @@
       </c>
       <c r="I45" s="15" t="n">
         <f aca="false">IF(B45="","",MAX(0,B45-$B$6))</f>
-        <v>1181563710</v>
+        <v>1178913710</v>
       </c>
     </row>
     <row r="46" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -2033,7 +2033,7 @@
       </c>
       <c r="I46" s="15" t="n">
         <f aca="false">IF(B46="","",MAX(0,B46-$B$6))</f>
-        <v>1381563710</v>
+        <v>1378913710</v>
       </c>
     </row>
     <row r="47" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -2061,7 +2061,7 @@
       </c>
       <c r="I47" s="15" t="n">
         <f aca="false">IF(B47="","",MAX(0,B47-$B$6))</f>
-        <v>1581563710</v>
+        <v>1578913710</v>
       </c>
     </row>
     <row r="48" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -2089,7 +2089,7 @@
       </c>
       <c r="I48" s="15" t="n">
         <f aca="false">IF(B48="","",MAX(0,B48-$B$6))</f>
-        <v>1781563710</v>
+        <v>1778913710</v>
       </c>
     </row>
     <row r="49" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -2117,7 +2117,7 @@
       </c>
       <c r="I49" s="15" t="n">
         <f aca="false">IF(B49="","",MAX(0,B49-$B$6))</f>
-        <v>1981563710</v>
+        <v>1978913710</v>
       </c>
     </row>
     <row r="50" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -2145,7 +2145,7 @@
       </c>
       <c r="I50" s="15" t="n">
         <f aca="false">IF(B50="","",MAX(0,B50-$B$6))</f>
-        <v>2181563710</v>
+        <v>2178913710</v>
       </c>
     </row>
     <row r="51" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -2173,7 +2173,7 @@
       </c>
       <c r="I51" s="15" t="n">
         <f aca="false">IF(B51="","",MAX(0,B51-$B$6))</f>
-        <v>2381563710</v>
+        <v>2378913710</v>
       </c>
     </row>
     <row r="52" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -2201,7 +2201,7 @@
       </c>
       <c r="I52" s="15" t="n">
         <f aca="false">IF(B52="","",MAX(0,B52-$B$6))</f>
-        <v>2581563710</v>
+        <v>2578913710</v>
       </c>
     </row>
     <row r="53" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -2229,7 +2229,7 @@
       </c>
       <c r="I53" s="15" t="n">
         <f aca="false">IF(B53="","",MAX(0,B53-$B$6))</f>
-        <v>2781563710</v>
+        <v>2778913710</v>
       </c>
     </row>
     <row r="54" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -2257,7 +2257,7 @@
       </c>
       <c r="I54" s="15" t="n">
         <f aca="false">IF(B54="","",MAX(0,B54-$B$6))</f>
-        <v>2981563710</v>
+        <v>2978913710</v>
       </c>
     </row>
     <row r="56" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -2388,11 +2388,11 @@
         <v>500000000</v>
       </c>
       <c r="E6" s="11" t="n">
-        <v>168895390</v>
+        <v>171545390</v>
       </c>
       <c r="F6" s="15" t="n">
         <f aca="false">IF(ISNUMBER(D6),MAX(0,D6-N(E6)),"")</f>
-        <v>331104610</v>
+        <v>328454610</v>
       </c>
       <c r="G6" s="11" t="n">
         <v>8240000</v>
@@ -3061,7 +3061,7 @@
       </c>
       <c r="B32" s="7" t="n">
         <f aca="false">SUM(E5:E30)</f>
-        <v>421146890</v>
+        <v>423796890</v>
       </c>
     </row>
     <row r="33" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -3079,7 +3079,7 @@
       </c>
       <c r="B34" s="7" t="n">
         <f aca="false">'Iso Fest'!B6</f>
-        <v>518436290</v>
+        <v>521086290</v>
       </c>
     </row>
     <row r="35" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -3097,7 +3097,7 @@
       </c>
       <c r="B36" s="7" t="n">
         <f aca="false">B34+B35</f>
-        <v>527831290</v>
+        <v>530481290</v>
       </c>
     </row>
     <row r="37" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -3115,7 +3115,7 @@
       </c>
       <c r="B38" s="7" t="n">
         <f aca="false">MAX(0,INDEX('Iso Fest'!B13:B54,'Iso Fest'!B9)-B36)</f>
-        <v>72168710</v>
+        <v>69518710</v>
       </c>
     </row>
     <row r="40" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">

--- a/Iso_Fest_Tracker.xlsx
+++ b/Iso_Fest_Tracker.xlsx
@@ -191,10 +191,10 @@
     <t xml:space="preserve">Maestro to 6 red stars</t>
   </si>
   <si>
+    <t xml:space="preserve">Knull to 7 red stars</t>
+  </si>
+  <si>
     <t xml:space="preserve">Not claimed</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Knull to 7 red stars</t>
   </si>
   <si>
     <t xml:space="preserve">Professor Xavier to 7 red stars</t>
@@ -960,22 +960,22 @@
         <v>9</v>
       </c>
       <c r="B6" s="6" t="n">
-        <v>521086290</v>
+        <v>525391290</v>
       </c>
       <c r="D6" s="4" t="s">
         <v>10</v>
       </c>
       <c r="E6" s="7" t="n">
         <f aca="false">SUMPRODUCT((A13:A54&lt;=$B$9)*(H13:H54&lt;&gt;"Claimed")*E13:E54)</f>
-        <v>2600000</v>
+        <v>1300000</v>
       </c>
       <c r="F6" s="7" t="n">
         <f aca="false">SUMPRODUCT((A13:A54&lt;=$B$9)*(H13:H54&lt;&gt;"Claimed")*F13:F54)</f>
-        <v>4200000</v>
+        <v>2800000</v>
       </c>
       <c r="G6" s="7" t="n">
         <f aca="false">SUMPRODUCT((A13:A54&lt;=$B$9)*(H13:H54&lt;&gt;"Claimed")*G13:G54)</f>
-        <v>5800000</v>
+        <v>3900000</v>
       </c>
     </row>
     <row r="7" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -984,7 +984,7 @@
       </c>
       <c r="B7" s="3" t="n">
         <f aca="false">IFERROR(INDEX(A13:A54,MATCH(TRUE(),INDEX(B13:B54&gt;B6,0),0)),"All done")</f>
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="D7" s="4" t="s">
         <v>12</v>
@@ -1008,7 +1008,7 @@
       </c>
       <c r="B8" s="7" t="n">
         <f aca="false">IFERROR(INDEX(I13:I54,MATCH(TRUE(),INDEX(B13:B54&gt;B6,0),0)),0)</f>
-        <v>3913710</v>
+        <v>24608710</v>
       </c>
     </row>
     <row r="9" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -1023,7 +1023,7 @@
       </c>
       <c r="G9" s="7" t="n">
         <f aca="false">Scoring!B36</f>
-        <v>530481290</v>
+        <v>534786290</v>
       </c>
     </row>
     <row r="10" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -1032,7 +1032,7 @@
       </c>
       <c r="B10" s="7" t="n">
         <f aca="false">MAX(0,INDEX(B13:B54,B9)-B6)</f>
-        <v>78913710</v>
+        <v>74608710</v>
       </c>
       <c r="D10" s="3" t="s">
         <v>17</v>
@@ -1048,7 +1048,7 @@
       </c>
       <c r="B11" s="7" t="n">
         <f aca="true">IFERROR(B10/MAX(B5-NOW(),0.01),0)</f>
-        <v>27986210.7267684</v>
+        <v>30462577.0191486</v>
       </c>
     </row>
     <row r="12" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -1741,11 +1741,11 @@
         <v>1900000</v>
       </c>
       <c r="H36" s="14" t="s">
-        <v>56</v>
+        <v>26</v>
       </c>
       <c r="I36" s="15" t="n">
         <f aca="false">IF(B36="","",MAX(0,B36-$B$6))</f>
-        <v>3913710</v>
+        <v>0</v>
       </c>
     </row>
     <row r="37" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -1756,7 +1756,7 @@
         <v>550000000</v>
       </c>
       <c r="C37" s="12" t="s">
-        <v>57</v>
+        <v>56</v>
       </c>
       <c r="D37" s="12" t="s">
         <v>43</v>
@@ -1771,11 +1771,11 @@
         <v>1900000</v>
       </c>
       <c r="H37" s="14" t="s">
-        <v>56</v>
+        <v>57</v>
       </c>
       <c r="I37" s="15" t="n">
         <f aca="false">IF(B37="","",MAX(0,B37-$B$6))</f>
-        <v>28913710</v>
+        <v>24608710</v>
       </c>
     </row>
     <row r="38" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -1799,11 +1799,11 @@
         <v>2000000</v>
       </c>
       <c r="H38" s="14" t="s">
-        <v>56</v>
+        <v>57</v>
       </c>
       <c r="I38" s="15" t="n">
         <f aca="false">IF(B38="","",MAX(0,B38-$B$6))</f>
-        <v>78913710</v>
+        <v>74608710</v>
       </c>
     </row>
     <row r="39" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -1829,11 +1829,11 @@
         <v>2000000</v>
       </c>
       <c r="H39" s="14" t="s">
-        <v>56</v>
+        <v>57</v>
       </c>
       <c r="I39" s="15" t="n">
         <f aca="false">IF(B39="","",MAX(0,B39-$B$6))</f>
-        <v>128913710</v>
+        <v>124608710</v>
       </c>
     </row>
     <row r="40" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -1857,11 +1857,11 @@
         <v>2000000</v>
       </c>
       <c r="H40" s="14" t="s">
-        <v>56</v>
+        <v>57</v>
       </c>
       <c r="I40" s="15" t="n">
         <f aca="false">IF(B40="","",MAX(0,B40-$B$6))</f>
-        <v>228913710</v>
+        <v>224608710</v>
       </c>
     </row>
     <row r="41" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -1887,11 +1887,11 @@
         <v>2000000</v>
       </c>
       <c r="H41" s="14" t="s">
-        <v>56</v>
+        <v>57</v>
       </c>
       <c r="I41" s="15" t="n">
         <f aca="false">IF(B41="","",MAX(0,B41-$B$6))</f>
-        <v>378913710</v>
+        <v>374608710</v>
       </c>
     </row>
     <row r="42" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -1915,11 +1915,11 @@
         <v>2000000</v>
       </c>
       <c r="H42" s="14" t="s">
-        <v>56</v>
+        <v>57</v>
       </c>
       <c r="I42" s="15" t="n">
         <f aca="false">IF(B42="","",MAX(0,B42-$B$6))</f>
-        <v>578913710</v>
+        <v>574608710</v>
       </c>
     </row>
     <row r="43" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -1945,11 +1945,11 @@
         <v>2000000</v>
       </c>
       <c r="H43" s="14" t="s">
-        <v>56</v>
+        <v>57</v>
       </c>
       <c r="I43" s="15" t="n">
         <f aca="false">IF(B43="","",MAX(0,B43-$B$6))</f>
-        <v>778913710</v>
+        <v>774608710</v>
       </c>
     </row>
     <row r="44" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -1973,11 +1973,11 @@
         <v>2700000</v>
       </c>
       <c r="H44" s="14" t="s">
-        <v>56</v>
+        <v>57</v>
       </c>
       <c r="I44" s="15" t="n">
         <f aca="false">IF(B44="","",MAX(0,B44-$B$6))</f>
-        <v>978913710</v>
+        <v>974608710</v>
       </c>
     </row>
     <row r="45" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -2001,11 +2001,11 @@
         <v>2700000</v>
       </c>
       <c r="H45" s="14" t="s">
-        <v>56</v>
+        <v>57</v>
       </c>
       <c r="I45" s="15" t="n">
         <f aca="false">IF(B45="","",MAX(0,B45-$B$6))</f>
-        <v>1178913710</v>
+        <v>1174608710</v>
       </c>
     </row>
     <row r="46" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -2029,11 +2029,11 @@
         <v>2700000</v>
       </c>
       <c r="H46" s="14" t="s">
-        <v>56</v>
+        <v>57</v>
       </c>
       <c r="I46" s="15" t="n">
         <f aca="false">IF(B46="","",MAX(0,B46-$B$6))</f>
-        <v>1378913710</v>
+        <v>1374608710</v>
       </c>
     </row>
     <row r="47" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -2057,11 +2057,11 @@
         <v>2700000</v>
       </c>
       <c r="H47" s="14" t="s">
-        <v>56</v>
+        <v>57</v>
       </c>
       <c r="I47" s="15" t="n">
         <f aca="false">IF(B47="","",MAX(0,B47-$B$6))</f>
-        <v>1578913710</v>
+        <v>1574608710</v>
       </c>
     </row>
     <row r="48" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -2085,11 +2085,11 @@
         <v>2700000</v>
       </c>
       <c r="H48" s="14" t="s">
-        <v>56</v>
+        <v>57</v>
       </c>
       <c r="I48" s="15" t="n">
         <f aca="false">IF(B48="","",MAX(0,B48-$B$6))</f>
-        <v>1778913710</v>
+        <v>1774608710</v>
       </c>
     </row>
     <row r="49" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -2113,11 +2113,11 @@
         <v>2700000</v>
       </c>
       <c r="H49" s="14" t="s">
-        <v>56</v>
+        <v>57</v>
       </c>
       <c r="I49" s="15" t="n">
         <f aca="false">IF(B49="","",MAX(0,B49-$B$6))</f>
-        <v>1978913710</v>
+        <v>1974608710</v>
       </c>
     </row>
     <row r="50" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -2141,11 +2141,11 @@
         <v>2700000</v>
       </c>
       <c r="H50" s="14" t="s">
-        <v>56</v>
+        <v>57</v>
       </c>
       <c r="I50" s="15" t="n">
         <f aca="false">IF(B50="","",MAX(0,B50-$B$6))</f>
-        <v>2178913710</v>
+        <v>2174608710</v>
       </c>
     </row>
     <row r="51" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -2169,11 +2169,11 @@
         <v>2700000</v>
       </c>
       <c r="H51" s="14" t="s">
-        <v>56</v>
+        <v>57</v>
       </c>
       <c r="I51" s="15" t="n">
         <f aca="false">IF(B51="","",MAX(0,B51-$B$6))</f>
-        <v>2378913710</v>
+        <v>2374608710</v>
       </c>
     </row>
     <row r="52" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -2197,11 +2197,11 @@
         <v>2700000</v>
       </c>
       <c r="H52" s="14" t="s">
-        <v>56</v>
+        <v>57</v>
       </c>
       <c r="I52" s="15" t="n">
         <f aca="false">IF(B52="","",MAX(0,B52-$B$6))</f>
-        <v>2578913710</v>
+        <v>2574608710</v>
       </c>
     </row>
     <row r="53" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -2225,11 +2225,11 @@
         <v>2700000</v>
       </c>
       <c r="H53" s="14" t="s">
-        <v>56</v>
+        <v>57</v>
       </c>
       <c r="I53" s="15" t="n">
         <f aca="false">IF(B53="","",MAX(0,B53-$B$6))</f>
-        <v>2778913710</v>
+        <v>2774608710</v>
       </c>
     </row>
     <row r="54" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -2253,11 +2253,11 @@
         <v>2700000</v>
       </c>
       <c r="H54" s="14" t="s">
-        <v>56</v>
+        <v>57</v>
       </c>
       <c r="I54" s="15" t="n">
         <f aca="false">IF(B54="","",MAX(0,B54-$B$6))</f>
-        <v>2978913710</v>
+        <v>2974608710</v>
       </c>
     </row>
     <row r="56" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -2388,11 +2388,11 @@
         <v>500000000</v>
       </c>
       <c r="E6" s="11" t="n">
-        <v>171545390</v>
+        <v>173945390</v>
       </c>
       <c r="F6" s="15" t="n">
         <f aca="false">IF(ISNUMBER(D6),MAX(0,D6-N(E6)),"")</f>
-        <v>328454610</v>
+        <v>326054610</v>
       </c>
       <c r="G6" s="11" t="n">
         <v>8240000</v>
@@ -3061,7 +3061,7 @@
       </c>
       <c r="B32" s="7" t="n">
         <f aca="false">SUM(E5:E30)</f>
-        <v>423796890</v>
+        <v>426196890</v>
       </c>
     </row>
     <row r="33" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -3070,7 +3070,7 @@
       </c>
       <c r="B33" s="7" t="n">
         <f aca="false">'Iso Fest'!B6-B32</f>
-        <v>97289400</v>
+        <v>99194400</v>
       </c>
     </row>
     <row r="34" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -3079,7 +3079,7 @@
       </c>
       <c r="B34" s="7" t="n">
         <f aca="false">'Iso Fest'!B6</f>
-        <v>521086290</v>
+        <v>525391290</v>
       </c>
     </row>
     <row r="35" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -3097,7 +3097,7 @@
       </c>
       <c r="B36" s="7" t="n">
         <f aca="false">B34+B35</f>
-        <v>530481290</v>
+        <v>534786290</v>
       </c>
     </row>
     <row r="37" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -3115,7 +3115,7 @@
       </c>
       <c r="B38" s="7" t="n">
         <f aca="false">MAX(0,INDEX('Iso Fest'!B13:B54,'Iso Fest'!B9)-B36)</f>
-        <v>69518710</v>
+        <v>65213710</v>
       </c>
     </row>
     <row r="40" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">

--- a/Iso_Fest_Tracker.xlsx
+++ b/Iso_Fest_Tracker.xlsx
@@ -960,7 +960,7 @@
         <v>9</v>
       </c>
       <c r="B6" s="6" t="n">
-        <v>525391290</v>
+        <v>533979590</v>
       </c>
       <c r="D6" s="4" t="s">
         <v>10</v>
@@ -1008,7 +1008,7 @@
       </c>
       <c r="B8" s="7" t="n">
         <f aca="false">IFERROR(INDEX(I13:I54,MATCH(TRUE(),INDEX(B13:B54&gt;B6,0),0)),0)</f>
-        <v>24608710</v>
+        <v>16020410</v>
       </c>
     </row>
     <row r="9" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -1023,7 +1023,7 @@
       </c>
       <c r="G9" s="7" t="n">
         <f aca="false">Scoring!B36</f>
-        <v>534786290</v>
+        <v>543374590</v>
       </c>
     </row>
     <row r="10" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -1032,7 +1032,7 @@
       </c>
       <c r="B10" s="7" t="n">
         <f aca="false">MAX(0,INDEX(B13:B54,B9)-B6)</f>
-        <v>74608710</v>
+        <v>66020410</v>
       </c>
       <c r="D10" s="3" t="s">
         <v>17</v>
@@ -1048,7 +1048,7 @@
       </c>
       <c r="B11" s="7" t="n">
         <f aca="true">IFERROR(B10/MAX(B5-NOW(),0.01),0)</f>
-        <v>30462577.0191486</v>
+        <v>28695179.3210574</v>
       </c>
     </row>
     <row r="12" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -1775,7 +1775,7 @@
       </c>
       <c r="I37" s="15" t="n">
         <f aca="false">IF(B37="","",MAX(0,B37-$B$6))</f>
-        <v>24608710</v>
+        <v>16020410</v>
       </c>
     </row>
     <row r="38" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -1803,7 +1803,7 @@
       </c>
       <c r="I38" s="15" t="n">
         <f aca="false">IF(B38="","",MAX(0,B38-$B$6))</f>
-        <v>74608710</v>
+        <v>66020410</v>
       </c>
     </row>
     <row r="39" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -1833,7 +1833,7 @@
       </c>
       <c r="I39" s="15" t="n">
         <f aca="false">IF(B39="","",MAX(0,B39-$B$6))</f>
-        <v>124608710</v>
+        <v>116020410</v>
       </c>
     </row>
     <row r="40" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -1861,7 +1861,7 @@
       </c>
       <c r="I40" s="15" t="n">
         <f aca="false">IF(B40="","",MAX(0,B40-$B$6))</f>
-        <v>224608710</v>
+        <v>216020410</v>
       </c>
     </row>
     <row r="41" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -1891,7 +1891,7 @@
       </c>
       <c r="I41" s="15" t="n">
         <f aca="false">IF(B41="","",MAX(0,B41-$B$6))</f>
-        <v>374608710</v>
+        <v>366020410</v>
       </c>
     </row>
     <row r="42" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -1919,7 +1919,7 @@
       </c>
       <c r="I42" s="15" t="n">
         <f aca="false">IF(B42="","",MAX(0,B42-$B$6))</f>
-        <v>574608710</v>
+        <v>566020410</v>
       </c>
     </row>
     <row r="43" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -1949,7 +1949,7 @@
       </c>
       <c r="I43" s="15" t="n">
         <f aca="false">IF(B43="","",MAX(0,B43-$B$6))</f>
-        <v>774608710</v>
+        <v>766020410</v>
       </c>
     </row>
     <row r="44" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -1977,7 +1977,7 @@
       </c>
       <c r="I44" s="15" t="n">
         <f aca="false">IF(B44="","",MAX(0,B44-$B$6))</f>
-        <v>974608710</v>
+        <v>966020410</v>
       </c>
     </row>
     <row r="45" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -2005,7 +2005,7 @@
       </c>
       <c r="I45" s="15" t="n">
         <f aca="false">IF(B45="","",MAX(0,B45-$B$6))</f>
-        <v>1174608710</v>
+        <v>1166020410</v>
       </c>
     </row>
     <row r="46" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -2033,7 +2033,7 @@
       </c>
       <c r="I46" s="15" t="n">
         <f aca="false">IF(B46="","",MAX(0,B46-$B$6))</f>
-        <v>1374608710</v>
+        <v>1366020410</v>
       </c>
     </row>
     <row r="47" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -2061,7 +2061,7 @@
       </c>
       <c r="I47" s="15" t="n">
         <f aca="false">IF(B47="","",MAX(0,B47-$B$6))</f>
-        <v>1574608710</v>
+        <v>1566020410</v>
       </c>
     </row>
     <row r="48" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -2089,7 +2089,7 @@
       </c>
       <c r="I48" s="15" t="n">
         <f aca="false">IF(B48="","",MAX(0,B48-$B$6))</f>
-        <v>1774608710</v>
+        <v>1766020410</v>
       </c>
     </row>
     <row r="49" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -2117,7 +2117,7 @@
       </c>
       <c r="I49" s="15" t="n">
         <f aca="false">IF(B49="","",MAX(0,B49-$B$6))</f>
-        <v>1974608710</v>
+        <v>1966020410</v>
       </c>
     </row>
     <row r="50" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -2145,7 +2145,7 @@
       </c>
       <c r="I50" s="15" t="n">
         <f aca="false">IF(B50="","",MAX(0,B50-$B$6))</f>
-        <v>2174608710</v>
+        <v>2166020410</v>
       </c>
     </row>
     <row r="51" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -2173,7 +2173,7 @@
       </c>
       <c r="I51" s="15" t="n">
         <f aca="false">IF(B51="","",MAX(0,B51-$B$6))</f>
-        <v>2374608710</v>
+        <v>2366020410</v>
       </c>
     </row>
     <row r="52" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -2201,7 +2201,7 @@
       </c>
       <c r="I52" s="15" t="n">
         <f aca="false">IF(B52="","",MAX(0,B52-$B$6))</f>
-        <v>2574608710</v>
+        <v>2566020410</v>
       </c>
     </row>
     <row r="53" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -2229,7 +2229,7 @@
       </c>
       <c r="I53" s="15" t="n">
         <f aca="false">IF(B53="","",MAX(0,B53-$B$6))</f>
-        <v>2774608710</v>
+        <v>2766020410</v>
       </c>
     </row>
     <row r="54" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -2257,7 +2257,7 @@
       </c>
       <c r="I54" s="15" t="n">
         <f aca="false">IF(B54="","",MAX(0,B54-$B$6))</f>
-        <v>2974608710</v>
+        <v>2966020410</v>
       </c>
     </row>
     <row r="56" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -2388,11 +2388,11 @@
         <v>500000000</v>
       </c>
       <c r="E6" s="11" t="n">
-        <v>173945390</v>
+        <v>176445390</v>
       </c>
       <c r="F6" s="15" t="n">
         <f aca="false">IF(ISNUMBER(D6),MAX(0,D6-N(E6)),"")</f>
-        <v>326054610</v>
+        <v>323554610</v>
       </c>
       <c r="G6" s="11" t="n">
         <v>8240000</v>
@@ -2419,11 +2419,11 @@
         <v>250000000</v>
       </c>
       <c r="E7" s="11" t="n">
-        <v>10750000</v>
+        <v>10850000</v>
       </c>
       <c r="F7" s="15" t="n">
         <f aca="false">IF(ISNUMBER(D7),MAX(0,D7-N(E7)),"")</f>
-        <v>239250000</v>
+        <v>239150000</v>
       </c>
       <c r="G7" s="11"/>
       <c r="H7" s="15" t="n">
@@ -3061,7 +3061,7 @@
       </c>
       <c r="B32" s="7" t="n">
         <f aca="false">SUM(E5:E30)</f>
-        <v>426196890</v>
+        <v>428796890</v>
       </c>
     </row>
     <row r="33" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -3070,7 +3070,7 @@
       </c>
       <c r="B33" s="7" t="n">
         <f aca="false">'Iso Fest'!B6-B32</f>
-        <v>99194400</v>
+        <v>105182700</v>
       </c>
     </row>
     <row r="34" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -3079,7 +3079,7 @@
       </c>
       <c r="B34" s="7" t="n">
         <f aca="false">'Iso Fest'!B6</f>
-        <v>525391290</v>
+        <v>533979590</v>
       </c>
     </row>
     <row r="35" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -3097,7 +3097,7 @@
       </c>
       <c r="B36" s="7" t="n">
         <f aca="false">B34+B35</f>
-        <v>534786290</v>
+        <v>543374590</v>
       </c>
     </row>
     <row r="37" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -3115,7 +3115,7 @@
       </c>
       <c r="B38" s="7" t="n">
         <f aca="false">MAX(0,INDEX('Iso Fest'!B13:B54,'Iso Fest'!B9)-B36)</f>
-        <v>65213710</v>
+        <v>56625410</v>
       </c>
     </row>
     <row r="40" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">

--- a/Iso_Fest_Tracker.xlsx
+++ b/Iso_Fest_Tracker.xlsx
@@ -960,7 +960,7 @@
         <v>9</v>
       </c>
       <c r="B6" s="6" t="n">
-        <v>533979590</v>
+        <v>544216140</v>
       </c>
       <c r="D6" s="4" t="s">
         <v>10</v>
@@ -1008,7 +1008,7 @@
       </c>
       <c r="B8" s="7" t="n">
         <f aca="false">IFERROR(INDEX(I13:I54,MATCH(TRUE(),INDEX(B13:B54&gt;B6,0),0)),0)</f>
-        <v>16020410</v>
+        <v>5783860</v>
       </c>
     </row>
     <row r="9" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -1023,7 +1023,7 @@
       </c>
       <c r="G9" s="7" t="n">
         <f aca="false">Scoring!B36</f>
-        <v>543374590</v>
+        <v>553611140</v>
       </c>
     </row>
     <row r="10" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -1032,14 +1032,14 @@
       </c>
       <c r="B10" s="7" t="n">
         <f aca="false">MAX(0,INDEX(B13:B54,B9)-B6)</f>
-        <v>66020410</v>
+        <v>55783860</v>
       </c>
       <c r="D10" s="3" t="s">
         <v>17</v>
       </c>
       <c r="G10" s="7" t="n">
         <f aca="false">Scoring!B37</f>
-        <v>24</v>
+        <v>25</v>
       </c>
     </row>
     <row r="11" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -1048,7 +1048,7 @@
       </c>
       <c r="B11" s="7" t="n">
         <f aca="true">IFERROR(B10/MAX(B5-NOW(),0.01),0)</f>
-        <v>28695179.3210574</v>
+        <v>39639575.2519736</v>
       </c>
     </row>
     <row r="12" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -1775,7 +1775,7 @@
       </c>
       <c r="I37" s="15" t="n">
         <f aca="false">IF(B37="","",MAX(0,B37-$B$6))</f>
-        <v>16020410</v>
+        <v>5783860</v>
       </c>
     </row>
     <row r="38" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -1803,7 +1803,7 @@
       </c>
       <c r="I38" s="15" t="n">
         <f aca="false">IF(B38="","",MAX(0,B38-$B$6))</f>
-        <v>66020410</v>
+        <v>55783860</v>
       </c>
     </row>
     <row r="39" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -1833,7 +1833,7 @@
       </c>
       <c r="I39" s="15" t="n">
         <f aca="false">IF(B39="","",MAX(0,B39-$B$6))</f>
-        <v>116020410</v>
+        <v>105783860</v>
       </c>
     </row>
     <row r="40" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -1861,7 +1861,7 @@
       </c>
       <c r="I40" s="15" t="n">
         <f aca="false">IF(B40="","",MAX(0,B40-$B$6))</f>
-        <v>216020410</v>
+        <v>205783860</v>
       </c>
     </row>
     <row r="41" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -1891,7 +1891,7 @@
       </c>
       <c r="I41" s="15" t="n">
         <f aca="false">IF(B41="","",MAX(0,B41-$B$6))</f>
-        <v>366020410</v>
+        <v>355783860</v>
       </c>
     </row>
     <row r="42" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -1919,7 +1919,7 @@
       </c>
       <c r="I42" s="15" t="n">
         <f aca="false">IF(B42="","",MAX(0,B42-$B$6))</f>
-        <v>566020410</v>
+        <v>555783860</v>
       </c>
     </row>
     <row r="43" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -1949,7 +1949,7 @@
       </c>
       <c r="I43" s="15" t="n">
         <f aca="false">IF(B43="","",MAX(0,B43-$B$6))</f>
-        <v>766020410</v>
+        <v>755783860</v>
       </c>
     </row>
     <row r="44" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -1977,7 +1977,7 @@
       </c>
       <c r="I44" s="15" t="n">
         <f aca="false">IF(B44="","",MAX(0,B44-$B$6))</f>
-        <v>966020410</v>
+        <v>955783860</v>
       </c>
     </row>
     <row r="45" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -2005,7 +2005,7 @@
       </c>
       <c r="I45" s="15" t="n">
         <f aca="false">IF(B45="","",MAX(0,B45-$B$6))</f>
-        <v>1166020410</v>
+        <v>1155783860</v>
       </c>
     </row>
     <row r="46" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -2033,7 +2033,7 @@
       </c>
       <c r="I46" s="15" t="n">
         <f aca="false">IF(B46="","",MAX(0,B46-$B$6))</f>
-        <v>1366020410</v>
+        <v>1355783860</v>
       </c>
     </row>
     <row r="47" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -2061,7 +2061,7 @@
       </c>
       <c r="I47" s="15" t="n">
         <f aca="false">IF(B47="","",MAX(0,B47-$B$6))</f>
-        <v>1566020410</v>
+        <v>1555783860</v>
       </c>
     </row>
     <row r="48" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -2089,7 +2089,7 @@
       </c>
       <c r="I48" s="15" t="n">
         <f aca="false">IF(B48="","",MAX(0,B48-$B$6))</f>
-        <v>1766020410</v>
+        <v>1755783860</v>
       </c>
     </row>
     <row r="49" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -2117,7 +2117,7 @@
       </c>
       <c r="I49" s="15" t="n">
         <f aca="false">IF(B49="","",MAX(0,B49-$B$6))</f>
-        <v>1966020410</v>
+        <v>1955783860</v>
       </c>
     </row>
     <row r="50" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -2145,7 +2145,7 @@
       </c>
       <c r="I50" s="15" t="n">
         <f aca="false">IF(B50="","",MAX(0,B50-$B$6))</f>
-        <v>2166020410</v>
+        <v>2155783860</v>
       </c>
     </row>
     <row r="51" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -2173,7 +2173,7 @@
       </c>
       <c r="I51" s="15" t="n">
         <f aca="false">IF(B51="","",MAX(0,B51-$B$6))</f>
-        <v>2366020410</v>
+        <v>2355783860</v>
       </c>
     </row>
     <row r="52" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -2201,7 +2201,7 @@
       </c>
       <c r="I52" s="15" t="n">
         <f aca="false">IF(B52="","",MAX(0,B52-$B$6))</f>
-        <v>2566020410</v>
+        <v>2555783860</v>
       </c>
     </row>
     <row r="53" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -2229,7 +2229,7 @@
       </c>
       <c r="I53" s="15" t="n">
         <f aca="false">IF(B53="","",MAX(0,B53-$B$6))</f>
-        <v>2766020410</v>
+        <v>2755783860</v>
       </c>
     </row>
     <row r="54" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -2257,7 +2257,7 @@
       </c>
       <c r="I54" s="15" t="n">
         <f aca="false">IF(B54="","",MAX(0,B54-$B$6))</f>
-        <v>2966020410</v>
+        <v>2955783860</v>
       </c>
     </row>
     <row r="56" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -2359,11 +2359,11 @@
         <v>51000000</v>
       </c>
       <c r="E5" s="11" t="n">
-        <v>45000000</v>
+        <v>48000000</v>
       </c>
       <c r="F5" s="15" t="n">
         <f aca="false">IF(ISNUMBER(D5),MAX(0,D5-N(E5)),"")</f>
-        <v>6000000</v>
+        <v>3000000</v>
       </c>
       <c r="G5" s="11"/>
       <c r="H5" s="15" t="n">
@@ -2388,11 +2388,11 @@
         <v>500000000</v>
       </c>
       <c r="E6" s="11" t="n">
-        <v>176445390</v>
+        <v>181991940</v>
       </c>
       <c r="F6" s="15" t="n">
         <f aca="false">IF(ISNUMBER(D6),MAX(0,D6-N(E6)),"")</f>
-        <v>323554610</v>
+        <v>318008060</v>
       </c>
       <c r="G6" s="11" t="n">
         <v>8240000</v>
@@ -3061,7 +3061,7 @@
       </c>
       <c r="B32" s="7" t="n">
         <f aca="false">SUM(E5:E30)</f>
-        <v>428796890</v>
+        <v>437343440</v>
       </c>
     </row>
     <row r="33" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -3070,7 +3070,7 @@
       </c>
       <c r="B33" s="7" t="n">
         <f aca="false">'Iso Fest'!B6-B32</f>
-        <v>105182700</v>
+        <v>106872700</v>
       </c>
     </row>
     <row r="34" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -3079,7 +3079,7 @@
       </c>
       <c r="B34" s="7" t="n">
         <f aca="false">'Iso Fest'!B6</f>
-        <v>533979590</v>
+        <v>544216140</v>
       </c>
     </row>
     <row r="35" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -3097,7 +3097,7 @@
       </c>
       <c r="B36" s="7" t="n">
         <f aca="false">B34+B35</f>
-        <v>543374590</v>
+        <v>553611140</v>
       </c>
     </row>
     <row r="37" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -3106,7 +3106,7 @@
       </c>
       <c r="B37" s="7" t="n">
         <f aca="false">IFERROR(INDEX('Iso Fest'!A13:A54,MATCH(B36,'Iso Fest'!B13:B54,1)),"Below milestone 15")</f>
-        <v>24</v>
+        <v>25</v>
       </c>
     </row>
     <row r="38" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -3115,7 +3115,7 @@
       </c>
       <c r="B38" s="7" t="n">
         <f aca="false">MAX(0,INDEX('Iso Fest'!B13:B54,'Iso Fest'!B9)-B36)</f>
-        <v>56625410</v>
+        <v>46388860</v>
       </c>
     </row>
     <row r="40" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
